--- a/Token_and_Data_Build_Out_v4_2.xlsx
+++ b/Token_and_Data_Build_Out_v4_2.xlsx
@@ -18,6 +18,7 @@
     <sheet name="Base" sheetId="3" r:id="rId3"/>
     <sheet name="Robo Bull" sheetId="4" r:id="rId4"/>
     <sheet name="Bear" sheetId="5" r:id="rId5"/>
+    <sheet name="Macro Levers" sheetId="6" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -17574,4 +17575,249 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="78" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Macro Levers (ITEM 8 / ITEM 9)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Edit column B. Read by dashboard + export.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>see</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>research/model_corrections_2026-06-23.md (defaults = committed base, 332.4 GW @ 2029)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>param_key</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>use_flops_demand</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1=ON: rebase demand on FLOPs (tokens x 2N). 0=committed token basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>flops_n_frontier_b</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>500</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>active params (billions), frontier tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>flops_n_mid_b</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>70</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>active params (billions), mid tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>flops_n_small_b</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>active params (billions), small tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>flops_mix2025_frontier</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.55</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025 token share, frontier</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>flops_mix2025_mid</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025 token share, mid</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>flops_mix2025_small</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.15</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025 token share, small</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>flops_mix2040_frontier</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.15</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2040 token share, frontier</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>flops_mix2040_mid</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.35</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2040 token share, mid</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>flops_mix2040_small</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2040 token share, small</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>flops_mfu</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.35</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>model FLOPs utilization (cancels in 2025 anchor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>capacity_retirement_rate</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ITEM 9: 0=plateau (base), 1=cliff, 0..1=controlled decline</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/Token_and_Data_Build_Out_v4_2.xlsx
+++ b/Token_and_Data_Build_Out_v4_2.xlsx
@@ -19,6 +19,7 @@
     <sheet name="Robo Bull" sheetId="4" r:id="rId4"/>
     <sheet name="Bear" sheetId="5" r:id="rId5"/>
     <sheet name="Macro Levers" sheetId="6" r:id="rId10"/>
+    <sheet name="FLOPs to Power" sheetId="7" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -17820,4 +17821,482 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10"/>
+    <col min="2" max="7" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>FLOPs to Power (committed-base snapshot, FLOPs basis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Regenerate: python research/refresh_flops_sheet_in_buildout.py (reflects Macro Levers tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>tokens_per_day_T</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>avg_N_active_B</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FLOPs_per_token</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FLOPs_per_day</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>fleet_TFLOP_per_W</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>power_GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2025</v>
+      </c>
+      <c r="B4">
+        <v>134.9</v>
+      </c>
+      <c r="C4">
+        <v>297</v>
+      </c>
+      <c r="D4">
+        <v>5.944e+11</v>
+      </c>
+      <c r="E4">
+        <v>8.0197756e+25</v>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2026</v>
+      </c>
+      <c r="B5">
+        <v>460.8</v>
+      </c>
+      <c r="C5">
+        <v>284</v>
+      </c>
+      <c r="D5">
+        <v>5.6857333e+11</v>
+      </c>
+      <c r="E5">
+        <v>2.6202362e+26</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2027</v>
+      </c>
+      <c r="B6">
+        <v>763.6</v>
+      </c>
+      <c r="C6">
+        <v>271</v>
+      </c>
+      <c r="D6">
+        <v>5.4274667e+11</v>
+      </c>
+      <c r="E6">
+        <v>4.1444856e+26</v>
+      </c>
+      <c r="F6">
+        <v>14</v>
+      </c>
+      <c r="G6">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2028</v>
+      </c>
+      <c r="B7">
+        <v>1359.8</v>
+      </c>
+      <c r="C7">
+        <v>258</v>
+      </c>
+      <c r="D7">
+        <v>5.1692e+11</v>
+      </c>
+      <c r="E7">
+        <v>7.0290923e+26</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2029</v>
+      </c>
+      <c r="B8">
+        <v>2172.8</v>
+      </c>
+      <c r="C8">
+        <v>246</v>
+      </c>
+      <c r="D8">
+        <v>4.9109333e+11</v>
+      </c>
+      <c r="E8">
+        <v>1.0670445e+27</v>
+      </c>
+      <c r="F8">
+        <v>21.5</v>
+      </c>
+      <c r="G8">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>2030</v>
+      </c>
+      <c r="B9">
+        <v>3253.6</v>
+      </c>
+      <c r="C9">
+        <v>233</v>
+      </c>
+      <c r="D9">
+        <v>4.6526667e+11</v>
+      </c>
+      <c r="E9">
+        <v>1.5137842e+27</v>
+      </c>
+      <c r="F9">
+        <v>25</v>
+      </c>
+      <c r="G9">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2031</v>
+      </c>
+      <c r="B10">
+        <v>4573</v>
+      </c>
+      <c r="C10">
+        <v>220</v>
+      </c>
+      <c r="D10">
+        <v>4.3944e+11</v>
+      </c>
+      <c r="E10">
+        <v>2.0095756e+27</v>
+      </c>
+      <c r="F10">
+        <v>28</v>
+      </c>
+      <c r="G10">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>2032</v>
+      </c>
+      <c r="B11">
+        <v>5901.4</v>
+      </c>
+      <c r="C11">
+        <v>207</v>
+      </c>
+      <c r="D11">
+        <v>4.1361333e+11</v>
+      </c>
+      <c r="E11">
+        <v>2.440905e+27</v>
+      </c>
+      <c r="F11">
+        <v>31</v>
+      </c>
+      <c r="G11">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>2033</v>
+      </c>
+      <c r="B12">
+        <v>7334.6</v>
+      </c>
+      <c r="C12">
+        <v>194</v>
+      </c>
+      <c r="D12">
+        <v>3.8778667e+11</v>
+      </c>
+      <c r="E12">
+        <v>2.8442663e+27</v>
+      </c>
+      <c r="F12">
+        <v>34</v>
+      </c>
+      <c r="G12">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>2034</v>
+      </c>
+      <c r="B13">
+        <v>8998.7</v>
+      </c>
+      <c r="C13">
+        <v>181</v>
+      </c>
+      <c r="D13">
+        <v>3.6196e+11</v>
+      </c>
+      <c r="E13">
+        <v>3.2571717e+27</v>
+      </c>
+      <c r="F13">
+        <v>37</v>
+      </c>
+      <c r="G13">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>2035</v>
+      </c>
+      <c r="B14">
+        <v>10620.4</v>
+      </c>
+      <c r="C14">
+        <v>168</v>
+      </c>
+      <c r="D14">
+        <v>3.3613333e+11</v>
+      </c>
+      <c r="E14">
+        <v>3.5698858e+27</v>
+      </c>
+      <c r="F14">
+        <v>40</v>
+      </c>
+      <c r="G14">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>2036</v>
+      </c>
+      <c r="B15">
+        <v>12433.3</v>
+      </c>
+      <c r="C15">
+        <v>155</v>
+      </c>
+      <c r="D15">
+        <v>3.1030667e+11</v>
+      </c>
+      <c r="E15">
+        <v>3.8581276e+27</v>
+      </c>
+      <c r="F15">
+        <v>42.9</v>
+      </c>
+      <c r="G15">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>2037</v>
+      </c>
+      <c r="B16">
+        <v>14482.7</v>
+      </c>
+      <c r="C16">
+        <v>142</v>
+      </c>
+      <c r="D16">
+        <v>2.8448e+11</v>
+      </c>
+      <c r="E16">
+        <v>4.120045e+27</v>
+      </c>
+      <c r="F16">
+        <v>45.7</v>
+      </c>
+      <c r="G16">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>2038</v>
+      </c>
+      <c r="B17">
+        <v>16709.1</v>
+      </c>
+      <c r="C17">
+        <v>129</v>
+      </c>
+      <c r="D17">
+        <v>2.5865333e+11</v>
+      </c>
+      <c r="E17">
+        <v>4.3218729e+27</v>
+      </c>
+      <c r="F17">
+        <v>48.6</v>
+      </c>
+      <c r="G17">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>2039</v>
+      </c>
+      <c r="B18">
+        <v>18373.4</v>
+      </c>
+      <c r="C18">
+        <v>116</v>
+      </c>
+      <c r="D18">
+        <v>2.3282667e+11</v>
+      </c>
+      <c r="E18">
+        <v>4.277828e+27</v>
+      </c>
+      <c r="F18">
+        <v>51.4</v>
+      </c>
+      <c r="G18">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>2040</v>
+      </c>
+      <c r="B19">
+        <v>20019.8</v>
+      </c>
+      <c r="C19">
+        <v>104</v>
+      </c>
+      <c r="D19">
+        <v>2.07e+11</v>
+      </c>
+      <c r="E19">
+        <v>4.1441009e+27</v>
+      </c>
+      <c r="F19">
+        <v>54.3</v>
+      </c>
+      <c r="G19">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>2041</v>
+      </c>
+      <c r="B20">
+        <v>21860.1</v>
+      </c>
+      <c r="C20">
+        <v>104</v>
+      </c>
+      <c r="D20">
+        <v>2.07e+11</v>
+      </c>
+      <c r="E20">
+        <v>4.5250457e+27</v>
+      </c>
+      <c r="F20">
+        <v>57.1</v>
+      </c>
+      <c r="G20">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>2042</v>
+      </c>
+      <c r="B21">
+        <v>23789.7</v>
+      </c>
+      <c r="C21">
+        <v>104</v>
+      </c>
+      <c r="D21">
+        <v>2.07e+11</v>
+      </c>
+      <c r="E21">
+        <v>4.9244656e+27</v>
+      </c>
+      <c r="F21">
+        <v>60</v>
+      </c>
+      <c r="G21">
+        <v>708</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/Token_and_Data_Build_Out_v4_2.xlsx
+++ b/Token_and_Data_Build_Out_v4_2.xlsx
@@ -21,7 +21,7 @@
     <sheet name="Macro Levers" sheetId="6" r:id="rId10"/>
     <sheet name="FLOPs to Power" sheetId="7" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -17825,476 +17825,722 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10"/>
-    <col min="2" max="7" width="18"/>
+    <col min="1" max="1" width="40"/>
+    <col min="2" max="9" width="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>FLOPs to Power (committed-base snapshot, FLOPs basis)</t>
+          <t>FLOPs to Power  ·  LIVE formulas (tokens -&gt; FLOPs -&gt; power)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regenerate: python research/refresh_flops_sheet_in_buildout.py (reflects Macro Levers tab)</t>
+          <t>Edit the inputs below; FLOPs and power recompute. Tokens are linked live to the 'Efficiency Overlay' sheet.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>anchor_GW_2025</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>retail_uplift_to_1400_user_basis</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>1400/'Efficiency Overlay'!C9-1</f>
+        <v>0.2727272727</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>capacity_retirement_rate_per_yr (ITEM 9: 0=plateau, 1=cliff)</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>training share = 6N FLOPs/token vs 2N inference. A CONSTANT split cancels in the re-anchor; VARY it by year to bend the power curve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
-          <t>tokens_per_day_T</t>
+          <t>tokens_day_T</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>training_share</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>avg_N_active_B</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>fleet_TFLOP_per_W</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>FLOPs_per_token</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>FLOPs_per_day</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
-          <t>fleet_TFLOP_per_W</t>
+          <t>power_raw_GW</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
-          <t>power_GW</t>
+          <t>power_GW_floored</t>
         </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>2025</v>
-      </c>
-      <c r="B4">
-        <v>134.9</v>
-      </c>
-      <c r="C4">
-        <v>297</v>
-      </c>
-      <c r="D4">
-        <v>5.944e+11</v>
-      </c>
-      <c r="E4">
-        <v>8.0197756e+25</v>
-      </c>
-      <c r="F4">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>2026</v>
-      </c>
-      <c r="B5">
-        <v>460.8</v>
-      </c>
-      <c r="C5">
-        <v>284</v>
-      </c>
-      <c r="D5">
-        <v>5.6857333e+11</v>
-      </c>
-      <c r="E5">
-        <v>2.6202362e+26</v>
-      </c>
-      <c r="F5">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>2027</v>
-      </c>
-      <c r="B6">
-        <v>763.6</v>
-      </c>
-      <c r="C6">
-        <v>271</v>
-      </c>
-      <c r="D6">
-        <v>5.4274667e+11</v>
-      </c>
-      <c r="E6">
-        <v>4.1444856e+26</v>
-      </c>
-      <c r="F6">
-        <v>14</v>
-      </c>
-      <c r="G6">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>2028</v>
-      </c>
-      <c r="B7">
-        <v>1359.8</v>
-      </c>
-      <c r="C7">
-        <v>258</v>
-      </c>
-      <c r="D7">
-        <v>5.1692e+11</v>
-      </c>
-      <c r="E7">
-        <v>7.0290923e+26</v>
-      </c>
-      <c r="F7">
-        <v>18</v>
-      </c>
-      <c r="G7">
-        <v>307</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="B8">
-        <v>2172.8</v>
+        <f>'Efficiency Overlay'!C5+'Efficiency Overlay'!C7*$B$4</f>
+        <v>134.9222</v>
       </c>
       <c r="C8">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>4.9109333e+11</v>
+        <v>297.2</v>
       </c>
       <c r="E8">
-        <v>1.0670445e+27</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>21.5</v>
+        <f>(2*(1-C8)+6*C8)*D8*1000000000</f>
+        <v>5.944e+11</v>
       </c>
       <c r="G8">
-        <v>390</v>
+        <f>B8*1000000000000*F8</f>
+        <v>8.019775568e+25</v>
+      </c>
+      <c r="H8">
+        <f>(G8/E8)/($G$8/$E$8)*$B$3</f>
+        <v>70</v>
+      </c>
+      <c r="I8">
+        <f>H8</f>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="B9">
-        <v>3253.6</v>
+        <f>'Efficiency Overlay'!D5+'Efficiency Overlay'!D7*$B$4</f>
+        <v>460.844025</v>
       </c>
       <c r="C9">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>4.6526667e+11</v>
+        <v>284.2866667</v>
       </c>
       <c r="E9">
-        <v>1.5137842e+27</v>
+        <v>11</v>
       </c>
       <c r="F9">
-        <v>25</v>
+        <f>(2*(1-C9)+6*C9)*D9*1000000000</f>
+        <v>5.685733333e+11</v>
       </c>
       <c r="G9">
-        <v>476</v>
+        <f>B9*1000000000000*F9</f>
+        <v>2.620236234e+26</v>
+      </c>
+      <c r="H9">
+        <f>(G9/E9)/($G$8/$E$8)*$B$3</f>
+        <v>187.1225372</v>
+      </c>
+      <c r="I9">
+        <f>MAX(H9,I8*(1-$B$5))</f>
+        <v>187.1225372</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>2031</v>
+        <v>2027</v>
       </c>
       <c r="B10">
-        <v>4573</v>
+        <f>'Efficiency Overlay'!E5+'Efficiency Overlay'!E7*$B$4</f>
+        <v>763.6132764</v>
       </c>
       <c r="C10">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>4.3944e+11</v>
+        <v>271.3733333</v>
       </c>
       <c r="E10">
-        <v>2.0095756e+27</v>
+        <v>14</v>
       </c>
       <c r="F10">
-        <v>28</v>
+        <f>(2*(1-C10)+6*C10)*D10*1000000000</f>
+        <v>5.427466667e+11</v>
       </c>
       <c r="G10">
-        <v>564</v>
+        <f>B10*1000000000000*F10</f>
+        <v>4.144485604e+26</v>
+      </c>
+      <c r="H10">
+        <f>(G10/E10)/($G$8/$E$8)*$B$3</f>
+        <v>232.5524581</v>
+      </c>
+      <c r="I10">
+        <f>MAX(H10,I9*(1-$B$5))</f>
+        <v>232.5524581</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>2032</v>
+        <v>2028</v>
       </c>
       <c r="B11">
-        <v>5901.4</v>
+        <f>'Efficiency Overlay'!F5+'Efficiency Overlay'!F7*$B$4</f>
+        <v>1359.802732</v>
       </c>
       <c r="C11">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>4.1361333e+11</v>
+        <v>258.46</v>
       </c>
       <c r="E11">
-        <v>2.440905e+27</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>31</v>
+        <f>(2*(1-C11)+6*C11)*D11*1000000000</f>
+        <v>5.1692e+11</v>
       </c>
       <c r="G11">
-        <v>619</v>
+        <f>B11*1000000000000*F11</f>
+        <v>7.029092283e+26</v>
+      </c>
+      <c r="H11">
+        <f>(G11/E11)/($G$8/$E$8)*$B$3</f>
+        <v>306.7644822</v>
+      </c>
+      <c r="I11">
+        <f>MAX(H11,I10*(1-$B$5))</f>
+        <v>306.7644822</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>2033</v>
+        <v>2029</v>
       </c>
       <c r="B12">
-        <v>7334.6</v>
+        <f>'Efficiency Overlay'!G5+'Efficiency Overlay'!G7*$B$4</f>
+        <v>2172.793754</v>
       </c>
       <c r="C12">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>3.8778667e+11</v>
+        <v>245.5466667</v>
       </c>
       <c r="E12">
-        <v>2.8442663e+27</v>
+        <v>21.5</v>
       </c>
       <c r="F12">
-        <v>34</v>
+        <f>(2*(1-C12)+6*C12)*D12*1000000000</f>
+        <v>4.910933333e+11</v>
       </c>
       <c r="G12">
-        <v>657</v>
+        <f>B12*1000000000000*F12</f>
+        <v>1.067044527e+27</v>
+      </c>
+      <c r="H12">
+        <f>(G12/E12)/($G$8/$E$8)*$B$3</f>
+        <v>389.8723335</v>
+      </c>
+      <c r="I12">
+        <f>MAX(H12,I11*(1-$B$5))</f>
+        <v>389.8723335</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="B13">
-        <v>8998.7</v>
+        <f>'Efficiency Overlay'!H5+'Efficiency Overlay'!H7*$B$4</f>
+        <v>3253.584075</v>
       </c>
       <c r="C13">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>3.6196e+11</v>
+        <v>232.6333333</v>
       </c>
       <c r="E13">
-        <v>3.2571717e+27</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>37</v>
+        <f>(2*(1-C13)+6*C13)*D13*1000000000</f>
+        <v>4.652666667e+11</v>
       </c>
       <c r="G13">
-        <v>692</v>
+        <f>B13*1000000000000*F13</f>
+        <v>1.513784217e+27</v>
+      </c>
+      <c r="H13">
+        <f>(G13/E13)/($G$8/$E$8)*$B$3</f>
+        <v>475.6662073</v>
+      </c>
+      <c r="I13">
+        <f>MAX(H13,I12*(1-$B$5))</f>
+        <v>475.6662073</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>2035</v>
+        <v>2031</v>
       </c>
       <c r="B14">
-        <v>10620.4</v>
+        <f>'Efficiency Overlay'!I5+'Efficiency Overlay'!I7*$B$4</f>
+        <v>4573.037415</v>
       </c>
       <c r="C14">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>3.3613333e+11</v>
+        <v>219.72</v>
       </c>
       <c r="E14">
-        <v>3.5698858e+27</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>40</v>
+        <f>(2*(1-C14)+6*C14)*D14*1000000000</f>
+        <v>4.3944e+11</v>
       </c>
       <c r="G14">
-        <v>701</v>
+        <f>B14*1000000000000*F14</f>
+        <v>2.009575562e+27</v>
+      </c>
+      <c r="H14">
+        <f>(G14/E14)/($G$8/$E$8)*$B$3</f>
+        <v>563.7994449</v>
+      </c>
+      <c r="I14">
+        <f>MAX(H14,I13*(1-$B$5))</f>
+        <v>563.7994449</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>2036</v>
+        <v>2032</v>
       </c>
       <c r="B15">
-        <v>12433.3</v>
+        <f>'Efficiency Overlay'!J5+'Efficiency Overlay'!J7*$B$4</f>
+        <v>5901.417522</v>
       </c>
       <c r="C15">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>3.1030667e+11</v>
+        <v>206.8066667</v>
       </c>
       <c r="E15">
-        <v>3.8581276e+27</v>
+        <v>31</v>
       </c>
       <c r="F15">
-        <v>42.9</v>
+        <f>(2*(1-C15)+6*C15)*D15*1000000000</f>
+        <v>4.136133333e+11</v>
       </c>
       <c r="G15">
-        <v>707</v>
+        <f>B15*1000000000000*F15</f>
+        <v>2.440904973e+27</v>
+      </c>
+      <c r="H15">
+        <f>(G15/E15)/($G$8/$E$8)*$B$3</f>
+        <v>618.5396054</v>
+      </c>
+      <c r="I15">
+        <f>MAX(H15,I14*(1-$B$5))</f>
+        <v>618.5396054</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>2037</v>
+        <v>2033</v>
       </c>
       <c r="B16">
-        <v>14482.7</v>
+        <f>'Efficiency Overlay'!K5+'Efficiency Overlay'!K7*$B$4</f>
+        <v>7334.615906</v>
       </c>
       <c r="C16">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>2.8448e+11</v>
+        <v>193.8933333</v>
       </c>
       <c r="E16">
-        <v>4.120045e+27</v>
+        <v>34</v>
       </c>
       <c r="F16">
-        <v>45.7</v>
+        <f>(2*(1-C16)+6*C16)*D16*1000000000</f>
+        <v>3.877866667e+11</v>
       </c>
       <c r="G16">
-        <v>708</v>
+        <f>B16*1000000000000*F16</f>
+        <v>2.844266254e+27</v>
+      </c>
+      <c r="H16">
+        <f>(G16/E16)/($G$8/$E$8)*$B$3</f>
+        <v>657.1577987</v>
+      </c>
+      <c r="I16">
+        <f>MAX(H16,I15*(1-$B$5))</f>
+        <v>657.1577987</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>2038</v>
+        <v>2034</v>
       </c>
       <c r="B17">
-        <v>16709.1</v>
+        <f>'Efficiency Overlay'!L5+'Efficiency Overlay'!L7*$B$4</f>
+        <v>8998.706093</v>
       </c>
       <c r="C17">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>2.5865333e+11</v>
+        <v>180.98</v>
       </c>
       <c r="E17">
-        <v>4.3218729e+27</v>
+        <v>37</v>
       </c>
       <c r="F17">
-        <v>48.6</v>
+        <f>(2*(1-C17)+6*C17)*D17*1000000000</f>
+        <v>3.6196e+11</v>
       </c>
       <c r="G17">
-        <v>708</v>
+        <f>B17*1000000000000*F17</f>
+        <v>3.257171657e+27</v>
+      </c>
+      <c r="H17">
+        <f>(G17/E17)/($G$8/$E$8)*$B$3</f>
+        <v>691.5399237</v>
+      </c>
+      <c r="I17">
+        <f>MAX(H17,I16*(1-$B$5))</f>
+        <v>691.5399237</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>2039</v>
+        <v>2035</v>
       </c>
       <c r="B18">
-        <v>18373.4</v>
+        <f>'Efficiency Overlay'!M5+'Efficiency Overlay'!M7*$B$4</f>
+        <v>10620.44566</v>
       </c>
       <c r="C18">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>2.3282667e+11</v>
+        <v>168.0666667</v>
       </c>
       <c r="E18">
-        <v>4.277828e+27</v>
+        <v>40</v>
       </c>
       <c r="F18">
-        <v>51.4</v>
+        <f>(2*(1-C18)+6*C18)*D18*1000000000</f>
+        <v>3.361333333e+11</v>
       </c>
       <c r="G18">
-        <v>708</v>
+        <f>B18*1000000000000*F18</f>
+        <v>3.569885802e+27</v>
+      </c>
+      <c r="H18">
+        <f>(G18/E18)/($G$8/$E$8)*$B$3</f>
+        <v>701.088215</v>
+      </c>
+      <c r="I18">
+        <f>MAX(H18,I17*(1-$B$5))</f>
+        <v>701.088215</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>2040</v>
+        <v>2036</v>
       </c>
       <c r="B19">
-        <v>20019.8</v>
+        <f>'Efficiency Overlay'!N5+'Efficiency Overlay'!N7*$B$4</f>
+        <v>12433.27321</v>
       </c>
       <c r="C19">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>2.07e+11</v>
+        <v>155.1533333</v>
       </c>
       <c r="E19">
-        <v>4.1441009e+27</v>
+        <v>42.85714286</v>
       </c>
       <c r="F19">
-        <v>54.3</v>
+        <f>(2*(1-C19)+6*C19)*D19*1000000000</f>
+        <v>3.103066667e+11</v>
       </c>
       <c r="G19">
-        <v>708</v>
+        <f>B19*1000000000000*F19</f>
+        <v>3.858127565e+27</v>
+      </c>
+      <c r="H19">
+        <f>(G19/E19)/($G$8/$E$8)*$B$3</f>
+        <v>707.1828223</v>
+      </c>
+      <c r="I19">
+        <f>MAX(H19,I18*(1-$B$5))</f>
+        <v>707.1828223</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>2041</v>
+        <v>2037</v>
       </c>
       <c r="B20">
-        <v>21860.1</v>
+        <f>'Efficiency Overlay'!O5+'Efficiency Overlay'!O7*$B$4</f>
+        <v>14482.72296</v>
       </c>
       <c r="C20">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>2.07e+11</v>
+        <v>142.24</v>
       </c>
       <c r="E20">
-        <v>4.5250457e+27</v>
+        <v>45.71428571</v>
       </c>
       <c r="F20">
-        <v>57.1</v>
+        <f>(2*(1-C20)+6*C20)*D20*1000000000</f>
+        <v>2.8448e+11</v>
       </c>
       <c r="G20">
-        <v>708</v>
+        <f>B20*1000000000000*F20</f>
+        <v>4.120045026e+27</v>
+      </c>
+      <c r="H20">
+        <f>(G20/E20)/($G$8/$E$8)*$B$3</f>
+        <v>707.9920135</v>
+      </c>
+      <c r="I20">
+        <f>MAX(H20,I19*(1-$B$5))</f>
+        <v>707.9920135</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
+        <v>2038</v>
+      </c>
+      <c r="B21">
+        <f>'Efficiency Overlay'!P5+'Efficiency Overlay'!P7*$B$4</f>
+        <v>16709.13265</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>129.3266667</v>
+      </c>
+      <c r="E21">
+        <v>48.57142857</v>
+      </c>
+      <c r="F21">
+        <f>(2*(1-C21)+6*C21)*D21*1000000000</f>
+        <v>2.586533333e+11</v>
+      </c>
+      <c r="G21">
+        <f>B21*1000000000000*F21</f>
+        <v>4.321872856e+27</v>
+      </c>
+      <c r="H21">
+        <f>(G21/E21)/($G$8/$E$8)*$B$3</f>
+        <v>698.9875558</v>
+      </c>
+      <c r="I21">
+        <f>MAX(H21,I20*(1-$B$5))</f>
+        <v>707.9920135</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>2039</v>
+      </c>
+      <c r="B22">
+        <f>'Efficiency Overlay'!Q5+'Efficiency Overlay'!Q7*$B$4</f>
+        <v>18373.44515</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>116.4133333</v>
+      </c>
+      <c r="E22">
+        <v>51.42857143</v>
+      </c>
+      <c r="F22">
+        <f>(2*(1-C22)+6*C22)*D22*1000000000</f>
+        <v>2.328266667e+11</v>
+      </c>
+      <c r="G22">
+        <f>B22*1000000000000*F22</f>
+        <v>4.27782799e+27</v>
+      </c>
+      <c r="H22">
+        <f>(G22/E22)/($G$8/$E$8)*$B$3</f>
+        <v>653.4271742</v>
+      </c>
+      <c r="I22">
+        <f>MAX(H22,I21*(1-$B$5))</f>
+        <v>707.9920135</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>2040</v>
+      </c>
+      <c r="B23">
+        <f>'Efficiency Overlay'!R5+'Efficiency Overlay'!R7*$B$4</f>
+        <v>20019.81107</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>103.5</v>
+      </c>
+      <c r="E23">
+        <v>54.28571429</v>
+      </c>
+      <c r="F23">
+        <f>(2*(1-C23)+6*C23)*D23*1000000000</f>
+        <v>2.07e+11</v>
+      </c>
+      <c r="G23">
+        <f>B23*1000000000000*F23</f>
+        <v>4.144100891e+27</v>
+      </c>
+      <c r="H23">
+        <f>(G23/E23)/($G$8/$E$8)*$B$3</f>
+        <v>599.6848788</v>
+      </c>
+      <c r="I23">
+        <f>MAX(H23,I22*(1-$B$5))</f>
+        <v>707.9920135</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>2041</v>
+      </c>
+      <c r="B24">
+        <f>'Efficiency Overlay'!S5+'Efficiency Overlay'!S7*$B$4</f>
+        <v>21860.12394</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>103.5</v>
+      </c>
+      <c r="E24">
+        <v>57.14285714</v>
+      </c>
+      <c r="F24">
+        <f>(2*(1-C24)+6*C24)*D24*1000000000</f>
+        <v>2.07e+11</v>
+      </c>
+      <c r="G24">
+        <f>B24*1000000000000*F24</f>
+        <v>4.525045655e+27</v>
+      </c>
+      <c r="H24">
+        <f>(G24/E24)/($G$8/$E$8)*$B$3</f>
+        <v>622.0701305</v>
+      </c>
+      <c r="I24">
+        <f>MAX(H24,I23*(1-$B$5))</f>
+        <v>707.9920135</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
         <v>2042</v>
       </c>
-      <c r="B21">
-        <v>23789.7</v>
-      </c>
-      <c r="C21">
-        <v>104</v>
-      </c>
-      <c r="D21">
+      <c r="B25">
+        <f>'Efficiency Overlay'!T5+'Efficiency Overlay'!T7*$B$4</f>
+        <v>23789.68866</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>103.5</v>
+      </c>
+      <c r="E25">
+        <v>60</v>
+      </c>
+      <c r="F25">
+        <f>(2*(1-C25)+6*C25)*D25*1000000000</f>
         <v>2.07e+11</v>
       </c>
-      <c r="E21">
-        <v>4.9244656e+27</v>
-      </c>
-      <c r="F21">
-        <v>60</v>
-      </c>
-      <c r="G21">
-        <v>708</v>
+      <c r="G25">
+        <f>B25*1000000000000*F25</f>
+        <v>4.924465553e+27</v>
+      </c>
+      <c r="H25">
+        <f>(G25/E25)/($G$8/$E$8)*$B$3</f>
+        <v>644.7423355</v>
+      </c>
+      <c r="I25">
+        <f>MAX(H25,I24*(1-$B$5))</f>
+        <v>707.9920135</v>
       </c>
     </row>
   </sheetData>

--- a/Token_and_Data_Build_Out_v4_2.xlsx
+++ b/Token_and_Data_Build_Out_v4_2.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Bear" sheetId="5" r:id="rId5"/>
     <sheet name="Macro Levers" sheetId="6" r:id="rId10"/>
     <sheet name="FLOPs to Power" sheetId="7" r:id="rId11"/>
+    <sheet name="Duration Lens" sheetId="8" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
@@ -18545,4 +18546,579 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D51"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="52"/>
+    <col min="2" max="4" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>AI POWER DEMAND  —  THE DURATION LENS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Token base (committed headline) vs the FLOPs lens. A token's power cost varies ~50x by model, so convert tokens -&gt; FLOPs -&gt; power. Live mechanics + stress-test inputs are on the 'FLOPs to Power' tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="47" t="inlineStr">
+        <is>
+          <t>1. THE QUESTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>How big does AI power demand get, and how long does the shortage last? FLOPs/token = 2 x active params; that is the honest power unit a token-count model cannot see (routing/orchestration moves it).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>2. THE CONVERSION  (one row = one year; full live version on 'FLOPs to Power')</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="47" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tokens/day (T)</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>'FLOPs to Power'!B8</f>
+        <v>134.9222</v>
+      </c>
+      <c r="C9">
+        <f>'FLOPs to Power'!B18</f>
+        <v>10620.446</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>x  FLOPs/token (2 x N_active)</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>'FLOPs to Power'!F8</f>
+        <v>5.944e+11</v>
+      </c>
+      <c r="C10">
+        <f>'FLOPs to Power'!F18</f>
+        <v>3.3613333e+11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>=  FLOPs/day</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>'FLOPs to Power'!G8</f>
+        <v>8.0197756e+25</v>
+      </c>
+      <c r="C11">
+        <f>'FLOPs to Power'!G18</f>
+        <v>3.5698858e+27</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>/  chip efficiency (TFLOP/W)</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>'FLOPs to Power'!E8</f>
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <f>'FLOPs to Power'!E18</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>=  power (GW)</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>'FLOPs to Power'!I8</f>
+        <v>70</v>
+      </c>
+      <c r="C13">
+        <f>'FLOPs to Power'!I18</f>
+        <v>701.08822</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="47" t="inlineStr">
+        <is>
+          <t>3. THE TUG-OF-WAR  (why power grows ~10x, not ~176x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tokens grow ~176x to 2042. But model size N falls ~3x (routing to smaller models) and chip TFLOP/W rises ~7x. Together they absorb most of it, so power grows ~10x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="47" t="inlineStr">
+        <is>
+          <t>4. TOKEN BASE  vs  FLOPs LENS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>Token base</t>
+        </is>
+      </c>
+      <c r="C19" s="47" t="inlineStr">
+        <is>
+          <t>FLOPs lens</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Peak gap (GW)</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>332</v>
+      </c>
+      <c r="C20">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Peak year</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>2029</v>
+      </c>
+      <c r="C21">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Demand floor 2042 (GW)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>549</v>
+      </c>
+      <c r="C22">
+        <f>'FLOPs to Power'!I25</f>
+        <v>708</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Gap closes (overshoot)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>2034</v>
+      </c>
+      <c r="C23">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>timing / peak</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>duration / higher floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="47" t="inlineStr">
+        <is>
+          <t>5. CHART THIS  (select A27:D45, then Insert &gt; Line Chart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="47" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B27" s="47" t="inlineStr">
+        <is>
+          <t>Token demand (GW)</t>
+        </is>
+      </c>
+      <c r="C27" s="47" t="inlineStr">
+        <is>
+          <t>FLOPs demand (GW)</t>
+        </is>
+      </c>
+      <c r="D27" s="47" t="inlineStr">
+        <is>
+          <t>Supply (GW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>2025</v>
+      </c>
+      <c r="B28">
+        <v>70</v>
+      </c>
+      <c r="C28">
+        <f>'FLOPs to Power'!I8</f>
+        <v>70</v>
+      </c>
+      <c r="D28">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>2026</v>
+      </c>
+      <c r="B29">
+        <v>219.2</v>
+      </c>
+      <c r="C29">
+        <f>'FLOPs to Power'!I9</f>
+        <v>187.1</v>
+      </c>
+      <c r="D29">
+        <v>85.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>2027</v>
+      </c>
+      <c r="B30">
+        <v>305.7</v>
+      </c>
+      <c r="C30">
+        <f>'FLOPs to Power'!I10</f>
+        <v>232.6</v>
+      </c>
+      <c r="D30">
+        <v>104.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>2028</v>
+      </c>
+      <c r="B31">
+        <v>427</v>
+      </c>
+      <c r="C31">
+        <f>'FLOPs to Power'!I11</f>
+        <v>306.8</v>
+      </c>
+      <c r="D31">
+        <v>135.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>2029</v>
+      </c>
+      <c r="B32">
+        <v>508.5</v>
+      </c>
+      <c r="C32">
+        <f>'FLOPs to Power'!I12</f>
+        <v>389.9</v>
+      </c>
+      <c r="D32">
+        <v>176.1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>2030</v>
+      </c>
+      <c r="B33">
+        <v>548.9</v>
+      </c>
+      <c r="C33">
+        <f>'FLOPs to Power'!I13</f>
+        <v>475.7</v>
+      </c>
+      <c r="D33">
+        <v>228.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>2031</v>
+      </c>
+      <c r="B34">
+        <v>548.9</v>
+      </c>
+      <c r="C34">
+        <f>'FLOPs to Power'!I14</f>
+        <v>563.8</v>
+      </c>
+      <c r="D34">
+        <v>286.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>2032</v>
+      </c>
+      <c r="B35">
+        <v>548.9</v>
+      </c>
+      <c r="C35">
+        <f>'FLOPs to Power'!I15</f>
+        <v>618.5</v>
+      </c>
+      <c r="D35">
+        <v>357.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>2033</v>
+      </c>
+      <c r="B36">
+        <v>548.9</v>
+      </c>
+      <c r="C36">
+        <f>'FLOPs to Power'!I16</f>
+        <v>657.2</v>
+      </c>
+      <c r="D36">
+        <v>447.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>2034</v>
+      </c>
+      <c r="B37">
+        <v>548.9</v>
+      </c>
+      <c r="C37">
+        <f>'FLOPs to Power'!I17</f>
+        <v>691.5</v>
+      </c>
+      <c r="D37">
+        <v>558.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>2035</v>
+      </c>
+      <c r="B38">
+        <v>548.9</v>
+      </c>
+      <c r="C38">
+        <f>'FLOPs to Power'!I18</f>
+        <v>701.1</v>
+      </c>
+      <c r="D38">
+        <v>698.6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>2036</v>
+      </c>
+      <c r="B39">
+        <v>548.9</v>
+      </c>
+      <c r="C39">
+        <f>'FLOPs to Power'!I19</f>
+        <v>707.2</v>
+      </c>
+      <c r="D39">
+        <v>803.3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>2037</v>
+      </c>
+      <c r="B40">
+        <v>548.9</v>
+      </c>
+      <c r="C40">
+        <f>'FLOPs to Power'!I20</f>
+        <v>708</v>
+      </c>
+      <c r="D40">
+        <v>923.8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>2038</v>
+      </c>
+      <c r="B41">
+        <v>548.9</v>
+      </c>
+      <c r="C41">
+        <f>'FLOPs to Power'!I21</f>
+        <v>708</v>
+      </c>
+      <c r="D41">
+        <v>1062.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>2039</v>
+      </c>
+      <c r="B42">
+        <v>548.9</v>
+      </c>
+      <c r="C42">
+        <f>'FLOPs to Power'!I22</f>
+        <v>708</v>
+      </c>
+      <c r="D42">
+        <v>1221.8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>2040</v>
+      </c>
+      <c r="B43">
+        <v>548.9</v>
+      </c>
+      <c r="C43">
+        <f>'FLOPs to Power'!I23</f>
+        <v>708</v>
+      </c>
+      <c r="D43">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>2041</v>
+      </c>
+      <c r="B44">
+        <v>548.9</v>
+      </c>
+      <c r="C44">
+        <f>'FLOPs to Power'!I24</f>
+        <v>708</v>
+      </c>
+      <c r="D44">
+        <v>1615.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>2042</v>
+      </c>
+      <c r="B45">
+        <v>548.9</v>
+      </c>
+      <c r="C45">
+        <f>'FLOPs to Power'!I25</f>
+        <v>708</v>
+      </c>
+      <c r="D45">
+        <v>1858.2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="47" t="inlineStr">
+        <is>
+          <t>6. STRESS-TEST IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Edit inputs on 'FLOPs to Power' (anchor, training share, N, TFLOP/W, retirement) — the FLOPs column above and this chart's FLOPs line update live. Broader levers on 'Macro Levers'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="47" t="inlineStr">
+        <is>
+          <t>7. THE TAKEAWAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>The FLOPs lens does NOT raise the peak (~278 vs 332). It raises the FLOOR (~708 vs 549, +29%) and extends the TIGHTNESS (gap closes ~2036 vs 2034). The power/grid/cooling case is about DURATION, not magnitude.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/Token_and_Data_Build_Out_v4_2.xlsx
+++ b/Token_and_Data_Build_Out_v4_2.xlsx
@@ -18621,67 +18621,67 @@
       </c>
       <c r="C9">
         <f>'FLOPs to Power'!B18</f>
-        <v>10620.446</v>
+        <v>10620.445661620677</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>x  FLOPs/token (2 x N_active)</t>
+          <t>x  FLOPs per token (2 x N_active)</t>
         </is>
       </c>
       <c r="B10">
         <f>'FLOPs to Power'!F8</f>
-        <v>5.944e+11</v>
+        <v>594400000000.0</v>
       </c>
       <c r="C10">
         <f>'FLOPs to Power'!F18</f>
-        <v>3.3613333e+11</v>
+        <v>336133333333.3334</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>=  FLOPs/day</t>
+          <t>-&gt;  FLOPs per day</t>
         </is>
       </c>
       <c r="B11">
         <f>'FLOPs to Power'!G8</f>
-        <v>8.0197756e+25</v>
+        <v>8.019775568e+25</v>
       </c>
       <c r="C11">
         <f>'FLOPs to Power'!G18</f>
-        <v>3.5698858e+27</v>
+        <v>3.569885801726098e+27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>/  chip efficiency (TFLOP/W)</t>
+          <t>/  chip efficiency (TFLOP per W)</t>
         </is>
       </c>
       <c r="B12">
         <f>'FLOPs to Power'!E8</f>
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="C12">
         <f>'FLOPs to Power'!E18</f>
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>=  power (GW)</t>
+          <t>-&gt;  power (GW)</t>
         </is>
       </c>
       <c r="B13">
         <f>'FLOPs to Power'!I8</f>
-        <v>70</v>
+        <v>70.0</v>
       </c>
       <c r="C13">
         <f>'FLOPs to Power'!I18</f>
-        <v>701.08822</v>
+        <v>701.0882150060941</v>
       </c>
     </row>
     <row r="15">
@@ -18758,7 +18758,7 @@
         <v>549</v>
       </c>
       <c r="C22">
-        <f>'FLOPs to Power'!I25</f>
+        <f>ROUND('FLOPs to Power'!I25,0)</f>
         <v>708</v>
       </c>
     </row>
@@ -18826,14 +18826,14 @@
         <v>2025</v>
       </c>
       <c r="B28">
-        <v>70</v>
+        <v>70.0</v>
       </c>
       <c r="C28">
-        <f>'FLOPs to Power'!I8</f>
-        <v>70</v>
+        <f>ROUND('FLOPs to Power'!I8,1)</f>
+        <v>70.0</v>
       </c>
       <c r="D28">
-        <v>70</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="29">
@@ -18844,7 +18844,7 @@
         <v>219.2</v>
       </c>
       <c r="C29">
-        <f>'FLOPs to Power'!I9</f>
+        <f>ROUND('FLOPs to Power'!I9,1)</f>
         <v>187.1</v>
       </c>
       <c r="D29">
@@ -18859,7 +18859,7 @@
         <v>305.7</v>
       </c>
       <c r="C30">
-        <f>'FLOPs to Power'!I10</f>
+        <f>ROUND('FLOPs to Power'!I10,1)</f>
         <v>232.6</v>
       </c>
       <c r="D30">
@@ -18871,10 +18871,10 @@
         <v>2028</v>
       </c>
       <c r="B31">
-        <v>427</v>
+        <v>427.0</v>
       </c>
       <c r="C31">
-        <f>'FLOPs to Power'!I11</f>
+        <f>ROUND('FLOPs to Power'!I11,1)</f>
         <v>306.8</v>
       </c>
       <c r="D31">
@@ -18889,7 +18889,7 @@
         <v>508.5</v>
       </c>
       <c r="C32">
-        <f>'FLOPs to Power'!I12</f>
+        <f>ROUND('FLOPs to Power'!I12,1)</f>
         <v>389.9</v>
       </c>
       <c r="D32">
@@ -18904,7 +18904,7 @@
         <v>548.9</v>
       </c>
       <c r="C33">
-        <f>'FLOPs to Power'!I13</f>
+        <f>ROUND('FLOPs to Power'!I13,1)</f>
         <v>475.7</v>
       </c>
       <c r="D33">
@@ -18919,7 +18919,7 @@
         <v>548.9</v>
       </c>
       <c r="C34">
-        <f>'FLOPs to Power'!I14</f>
+        <f>ROUND('FLOPs to Power'!I14,1)</f>
         <v>563.8</v>
       </c>
       <c r="D34">
@@ -18934,7 +18934,7 @@
         <v>548.9</v>
       </c>
       <c r="C35">
-        <f>'FLOPs to Power'!I15</f>
+        <f>ROUND('FLOPs to Power'!I15,1)</f>
         <v>618.5</v>
       </c>
       <c r="D35">
@@ -18949,7 +18949,7 @@
         <v>548.9</v>
       </c>
       <c r="C36">
-        <f>'FLOPs to Power'!I16</f>
+        <f>ROUND('FLOPs to Power'!I16,1)</f>
         <v>657.2</v>
       </c>
       <c r="D36">
@@ -18964,7 +18964,7 @@
         <v>548.9</v>
       </c>
       <c r="C37">
-        <f>'FLOPs to Power'!I17</f>
+        <f>ROUND('FLOPs to Power'!I17,1)</f>
         <v>691.5</v>
       </c>
       <c r="D37">
@@ -18979,7 +18979,7 @@
         <v>548.9</v>
       </c>
       <c r="C38">
-        <f>'FLOPs to Power'!I18</f>
+        <f>ROUND('FLOPs to Power'!I18,1)</f>
         <v>701.1</v>
       </c>
       <c r="D38">
@@ -18994,7 +18994,7 @@
         <v>548.9</v>
       </c>
       <c r="C39">
-        <f>'FLOPs to Power'!I19</f>
+        <f>ROUND('FLOPs to Power'!I19,1)</f>
         <v>707.2</v>
       </c>
       <c r="D39">
@@ -19009,8 +19009,8 @@
         <v>548.9</v>
       </c>
       <c r="C40">
-        <f>'FLOPs to Power'!I20</f>
-        <v>708</v>
+        <f>ROUND('FLOPs to Power'!I20,1)</f>
+        <v>708.0</v>
       </c>
       <c r="D40">
         <v>923.8</v>
@@ -19024,8 +19024,8 @@
         <v>548.9</v>
       </c>
       <c r="C41">
-        <f>'FLOPs to Power'!I21</f>
-        <v>708</v>
+        <f>ROUND('FLOPs to Power'!I21,1)</f>
+        <v>708.0</v>
       </c>
       <c r="D41">
         <v>1062.4</v>
@@ -19039,8 +19039,8 @@
         <v>548.9</v>
       </c>
       <c r="C42">
-        <f>'FLOPs to Power'!I22</f>
-        <v>708</v>
+        <f>ROUND('FLOPs to Power'!I22,1)</f>
+        <v>708.0</v>
       </c>
       <c r="D42">
         <v>1221.8</v>
@@ -19054,11 +19054,11 @@
         <v>548.9</v>
       </c>
       <c r="C43">
-        <f>'FLOPs to Power'!I23</f>
-        <v>708</v>
+        <f>ROUND('FLOPs to Power'!I23,1)</f>
+        <v>708.0</v>
       </c>
       <c r="D43">
-        <v>1405</v>
+        <v>1405.0</v>
       </c>
     </row>
     <row r="44">
@@ -19069,8 +19069,8 @@
         <v>548.9</v>
       </c>
       <c r="C44">
-        <f>'FLOPs to Power'!I24</f>
-        <v>708</v>
+        <f>ROUND('FLOPs to Power'!I24,1)</f>
+        <v>708.0</v>
       </c>
       <c r="D44">
         <v>1615.8</v>
@@ -19084,8 +19084,8 @@
         <v>548.9</v>
       </c>
       <c r="C45">
-        <f>'FLOPs to Power'!I25</f>
-        <v>708</v>
+        <f>ROUND('FLOPs to Power'!I25,1)</f>
+        <v>708.0</v>
       </c>
       <c r="D45">
         <v>1858.2</v>

--- a/Token_and_Data_Build_Out_v4_2.xlsx
+++ b/Token_and_Data_Build_Out_v4_2.xlsx
@@ -21,6 +21,7 @@
     <sheet name="Macro Levers" sheetId="6" r:id="rId10"/>
     <sheet name="FLOPs to Power" sheetId="7" r:id="rId11"/>
     <sheet name="Duration Lens" sheetId="8" r:id="rId12"/>
+    <sheet name="Operating Model" sheetId="9" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
@@ -17854,7 +17855,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>70</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="4">
@@ -17865,7 +17866,7 @@
       </c>
       <c r="B4">
         <f>1400/'Efficiency Overlay'!C9-1</f>
-        <v>0.2727272727</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="5">
@@ -17875,7 +17876,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -17941,17 +17942,17 @@
         <v>134.9222</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D8">
         <v>297.2</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="F8">
         <f>(2*(1-C8)+6*C8)*D8*1000000000</f>
-        <v>5.944e+11</v>
+        <v>594400000000.0</v>
       </c>
       <c r="G8">
         <f>B8*1000000000000*F8</f>
@@ -17959,11 +17960,11 @@
       </c>
       <c r="H8">
         <f>(G8/E8)/($G$8/$E$8)*$B$3</f>
-        <v>70</v>
+        <v>70.0</v>
       </c>
       <c r="I8">
         <f>H8</f>
-        <v>70</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="9">
@@ -17975,29 +17976,29 @@
         <v>460.844025</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D9">
-        <v>284.2866667</v>
+        <v>284.28666666666675</v>
       </c>
       <c r="E9">
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="F9">
         <f>(2*(1-C9)+6*C9)*D9*1000000000</f>
-        <v>5.685733333e+11</v>
+        <v>568573333333.3335</v>
       </c>
       <c r="G9">
         <f>B9*1000000000000*F9</f>
-        <v>2.620236234e+26</v>
+        <v>2.6202362344100007e+26</v>
       </c>
       <c r="H9">
         <f>(G9/E9)/($G$8/$E$8)*$B$3</f>
-        <v>187.1225372</v>
+        <v>187.122537246895</v>
       </c>
       <c r="I9">
         <f>MAX(H9,I8*(1-$B$5))</f>
-        <v>187.1225372</v>
+        <v>187.122537246895</v>
       </c>
     </row>
     <row r="10">
@@ -18006,32 +18007,32 @@
       </c>
       <c r="B10">
         <f>'Efficiency Overlay'!E5+'Efficiency Overlay'!E7*$B$4</f>
-        <v>763.6132764</v>
+        <v>763.613276375</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D10">
-        <v>271.3733333</v>
+        <v>271.37333333333333</v>
       </c>
       <c r="E10">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="F10">
         <f>(2*(1-C10)+6*C10)*D10*1000000000</f>
-        <v>5.427466667e+11</v>
+        <v>542746666666.6667</v>
       </c>
       <c r="G10">
         <f>B10*1000000000000*F10</f>
-        <v>4.144485604e+26</v>
+        <v>4.144485603749434e+26</v>
       </c>
       <c r="H10">
         <f>(G10/E10)/($G$8/$E$8)*$B$3</f>
-        <v>232.5524581</v>
+        <v>232.55245809233412</v>
       </c>
       <c r="I10">
         <f>MAX(H10,I9*(1-$B$5))</f>
-        <v>232.5524581</v>
+        <v>232.55245809233412</v>
       </c>
     </row>
     <row r="11">
@@ -18040,32 +18041,32 @@
       </c>
       <c r="B11">
         <f>'Efficiency Overlay'!F5+'Efficiency Overlay'!F7*$B$4</f>
-        <v>1359.802732</v>
+        <v>1359.8027322304688</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D11">
-        <v>258.46</v>
+        <v>258.46000000000004</v>
       </c>
       <c r="E11">
-        <v>18</v>
+        <v>18.0</v>
       </c>
       <c r="F11">
         <f>(2*(1-C11)+6*C11)*D11*1000000000</f>
-        <v>5.1692e+11</v>
+        <v>516920000000.00006</v>
       </c>
       <c r="G11">
         <f>B11*1000000000000*F11</f>
-        <v>7.029092283e+26</v>
+        <v>7.029092283445739e+26</v>
       </c>
       <c r="H11">
         <f>(G11/E11)/($G$8/$E$8)*$B$3</f>
-        <v>306.7644822</v>
+        <v>306.7644821661184</v>
       </c>
       <c r="I11">
         <f>MAX(H11,I10*(1-$B$5))</f>
-        <v>306.7644822</v>
+        <v>306.7644821661184</v>
       </c>
     </row>
     <row r="12">
@@ -18074,32 +18075,32 @@
       </c>
       <c r="B12">
         <f>'Efficiency Overlay'!G5+'Efficiency Overlay'!G7*$B$4</f>
-        <v>2172.793754</v>
+        <v>2172.793753804055</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D12">
-        <v>245.5466667</v>
+        <v>245.54666666666668</v>
       </c>
       <c r="E12">
         <v>21.5</v>
       </c>
       <c r="F12">
         <f>(2*(1-C12)+6*C12)*D12*1000000000</f>
-        <v>4.910933333e+11</v>
+        <v>491093333333.3334</v>
       </c>
       <c r="G12">
         <f>B12*1000000000000*F12</f>
-        <v>1.067044527e+27</v>
+        <v>1.0670445272014794e+27</v>
       </c>
       <c r="H12">
         <f>(G12/E12)/($G$8/$E$8)*$B$3</f>
-        <v>389.8723335</v>
+        <v>389.8723334685694</v>
       </c>
       <c r="I12">
         <f>MAX(H12,I11*(1-$B$5))</f>
-        <v>389.8723335</v>
+        <v>389.8723334685694</v>
       </c>
     </row>
     <row r="13">
@@ -18108,32 +18109,32 @@
       </c>
       <c r="B13">
         <f>'Efficiency Overlay'!H5+'Efficiency Overlay'!H7*$B$4</f>
-        <v>3253.584075</v>
+        <v>3253.5840749501463</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D13">
-        <v>232.6333333</v>
+        <v>232.63333333333338</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="F13">
         <f>(2*(1-C13)+6*C13)*D13*1000000000</f>
-        <v>4.652666667e+11</v>
+        <v>465266666666.66675</v>
       </c>
       <c r="G13">
         <f>B13*1000000000000*F13</f>
-        <v>1.513784217e+27</v>
+        <v>1.513784217271805e+27</v>
       </c>
       <c r="H13">
         <f>(G13/E13)/($G$8/$E$8)*$B$3</f>
-        <v>475.6662073</v>
+        <v>475.6662072622415</v>
       </c>
       <c r="I13">
         <f>MAX(H13,I12*(1-$B$5))</f>
-        <v>475.6662073</v>
+        <v>475.6662072622415</v>
       </c>
     </row>
     <row r="14">
@@ -18142,32 +18143,32 @@
       </c>
       <c r="B14">
         <f>'Efficiency Overlay'!I5+'Efficiency Overlay'!I7*$B$4</f>
-        <v>4573.037415</v>
+        <v>4573.0374147267485</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D14">
         <v>219.72</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>28.0</v>
       </c>
       <c r="F14">
         <f>(2*(1-C14)+6*C14)*D14*1000000000</f>
-        <v>4.3944e+11</v>
+        <v>439440000000.0</v>
       </c>
       <c r="G14">
         <f>B14*1000000000000*F14</f>
-        <v>2.009575562e+27</v>
+        <v>2.009575561527522e+27</v>
       </c>
       <c r="H14">
         <f>(G14/E14)/($G$8/$E$8)*$B$3</f>
-        <v>563.7994449</v>
+        <v>563.7994448970002</v>
       </c>
       <c r="I14">
         <f>MAX(H14,I13*(1-$B$5))</f>
-        <v>563.7994449</v>
+        <v>563.7994448970002</v>
       </c>
     </row>
     <row r="15">
@@ -18176,32 +18177,32 @@
       </c>
       <c r="B15">
         <f>'Efficiency Overlay'!J5+'Efficiency Overlay'!J7*$B$4</f>
-        <v>5901.417522</v>
+        <v>5901.417521751226</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D15">
-        <v>206.8066667</v>
+        <v>206.80666666666667</v>
       </c>
       <c r="E15">
-        <v>31</v>
+        <v>31.0</v>
       </c>
       <c r="F15">
         <f>(2*(1-C15)+6*C15)*D15*1000000000</f>
-        <v>4.136133333e+11</v>
+        <v>413613333333.3334</v>
       </c>
       <c r="G15">
         <f>B15*1000000000000*F15</f>
-        <v>2.440904973e+27</v>
+        <v>2.440904972563264e+27</v>
       </c>
       <c r="H15">
         <f>(G15/E15)/($G$8/$E$8)*$B$3</f>
-        <v>618.5396054</v>
+        <v>618.5396053977472</v>
       </c>
       <c r="I15">
         <f>MAX(H15,I14*(1-$B$5))</f>
-        <v>618.5396054</v>
+        <v>618.5396053977472</v>
       </c>
     </row>
     <row r="16">
@@ -18210,32 +18211,32 @@
       </c>
       <c r="B16">
         <f>'Efficiency Overlay'!K5+'Efficiency Overlay'!K7*$B$4</f>
-        <v>7334.615906</v>
+        <v>7334.615906104267</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D16">
-        <v>193.8933333</v>
+        <v>193.89333333333335</v>
       </c>
       <c r="E16">
-        <v>34</v>
+        <v>34.0</v>
       </c>
       <c r="F16">
         <f>(2*(1-C16)+6*C16)*D16*1000000000</f>
-        <v>3.877866667e+11</v>
+        <v>387786666666.6667</v>
       </c>
       <c r="G16">
         <f>B16*1000000000000*F16</f>
-        <v>2.844266254e+27</v>
+        <v>2.8442662535084867e+27</v>
       </c>
       <c r="H16">
         <f>(G16/E16)/($G$8/$E$8)*$B$3</f>
-        <v>657.1577987</v>
+        <v>657.1577986546976</v>
       </c>
       <c r="I16">
         <f>MAX(H16,I15*(1-$B$5))</f>
-        <v>657.1577987</v>
+        <v>657.1577986546976</v>
       </c>
     </row>
     <row r="17">
@@ -18244,32 +18245,32 @@
       </c>
       <c r="B17">
         <f>'Efficiency Overlay'!L5+'Efficiency Overlay'!L7*$B$4</f>
-        <v>8998.706093</v>
+        <v>8998.706093065295</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D17">
-        <v>180.98</v>
+        <v>180.98000000000002</v>
       </c>
       <c r="E17">
-        <v>37</v>
+        <v>37.0</v>
       </c>
       <c r="F17">
         <f>(2*(1-C17)+6*C17)*D17*1000000000</f>
-        <v>3.6196e+11</v>
+        <v>361960000000.00006</v>
       </c>
       <c r="G17">
         <f>B17*1000000000000*F17</f>
-        <v>3.257171657e+27</v>
+        <v>3.2571716574459146e+27</v>
       </c>
       <c r="H17">
         <f>(G17/E17)/($G$8/$E$8)*$B$3</f>
-        <v>691.5399237</v>
+        <v>691.539923689271</v>
       </c>
       <c r="I17">
         <f>MAX(H17,I16*(1-$B$5))</f>
-        <v>691.5399237</v>
+        <v>691.539923689271</v>
       </c>
     </row>
     <row r="18">
@@ -18278,32 +18279,32 @@
       </c>
       <c r="B18">
         <f>'Efficiency Overlay'!M5+'Efficiency Overlay'!M7*$B$4</f>
-        <v>10620.44566</v>
+        <v>10620.445661620677</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D18">
-        <v>168.0666667</v>
+        <v>168.0666666666667</v>
       </c>
       <c r="E18">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="F18">
         <f>(2*(1-C18)+6*C18)*D18*1000000000</f>
-        <v>3.361333333e+11</v>
+        <v>336133333333.3334</v>
       </c>
       <c r="G18">
         <f>B18*1000000000000*F18</f>
-        <v>3.569885802e+27</v>
+        <v>3.5698858017260976e+27</v>
       </c>
       <c r="H18">
         <f>(G18/E18)/($G$8/$E$8)*$B$3</f>
-        <v>701.088215</v>
+        <v>701.0882150060941</v>
       </c>
       <c r="I18">
         <f>MAX(H18,I17*(1-$B$5))</f>
-        <v>701.088215</v>
+        <v>701.0882150060941</v>
       </c>
     </row>
     <row r="19">
@@ -18312,32 +18313,32 @@
       </c>
       <c r="B19">
         <f>'Efficiency Overlay'!N5+'Efficiency Overlay'!N7*$B$4</f>
-        <v>12433.27321</v>
+        <v>12433.27320756883</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D19">
-        <v>155.1533333</v>
+        <v>155.15333333333334</v>
       </c>
       <c r="E19">
-        <v>42.85714286</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="F19">
         <f>(2*(1-C19)+6*C19)*D19*1000000000</f>
-        <v>3.103066667e+11</v>
+        <v>310306666666.6667</v>
       </c>
       <c r="G19">
         <f>B19*1000000000000*F19</f>
-        <v>3.858127565e+27</v>
+        <v>3.858127564796659e+27</v>
       </c>
       <c r="H19">
         <f>(G19/E19)/($G$8/$E$8)*$B$3</f>
-        <v>707.1828223</v>
+        <v>707.1828222825759</v>
       </c>
       <c r="I19">
         <f>MAX(H19,I18*(1-$B$5))</f>
-        <v>707.1828223</v>
+        <v>707.1828222825759</v>
       </c>
     </row>
     <row r="20">
@@ -18346,32 +18347,32 @@
       </c>
       <c r="B20">
         <f>'Efficiency Overlay'!O5+'Efficiency Overlay'!O7*$B$4</f>
-        <v>14482.72296</v>
+        <v>14482.722955550775</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D20">
         <v>142.24</v>
       </c>
       <c r="E20">
-        <v>45.71428571</v>
+        <v>45.714285714285715</v>
       </c>
       <c r="F20">
         <f>(2*(1-C20)+6*C20)*D20*1000000000</f>
-        <v>2.8448e+11</v>
+        <v>284480000000.0</v>
       </c>
       <c r="G20">
         <f>B20*1000000000000*F20</f>
-        <v>4.120045026e+27</v>
+        <v>4.1200450263950844e+27</v>
       </c>
       <c r="H20">
         <f>(G20/E20)/($G$8/$E$8)*$B$3</f>
-        <v>707.9920135</v>
+        <v>707.9920134743508</v>
       </c>
       <c r="I20">
         <f>MAX(H20,I19*(1-$B$5))</f>
-        <v>707.9920135</v>
+        <v>707.9920134743508</v>
       </c>
     </row>
     <row r="21">
@@ -18380,32 +18381,32 @@
       </c>
       <c r="B21">
         <f>'Efficiency Overlay'!P5+'Efficiency Overlay'!P7*$B$4</f>
-        <v>16709.13265</v>
+        <v>16709.132646039423</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D21">
-        <v>129.3266667</v>
+        <v>129.32666666666668</v>
       </c>
       <c r="E21">
-        <v>48.57142857</v>
+        <v>48.57142857142857</v>
       </c>
       <c r="F21">
         <f>(2*(1-C21)+6*C21)*D21*1000000000</f>
-        <v>2.586533333e+11</v>
+        <v>258653333333.33337</v>
       </c>
       <c r="G21">
         <f>B21*1000000000000*F21</f>
-        <v>4.321872856e+27</v>
+        <v>4.3218728560069174e+27</v>
       </c>
       <c r="H21">
         <f>(G21/E21)/($G$8/$E$8)*$B$3</f>
-        <v>698.9875558</v>
+        <v>698.9875557644821</v>
       </c>
       <c r="I21">
         <f>MAX(H21,I20*(1-$B$5))</f>
-        <v>707.9920135</v>
+        <v>707.9920134743508</v>
       </c>
     </row>
     <row r="22">
@@ -18414,32 +18415,32 @@
       </c>
       <c r="B22">
         <f>'Efficiency Overlay'!Q5+'Efficiency Overlay'!Q7*$B$4</f>
-        <v>18373.44515</v>
+        <v>18373.445150193562</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D22">
-        <v>116.4133333</v>
+        <v>116.41333333333334</v>
       </c>
       <c r="E22">
-        <v>51.42857143</v>
+        <v>51.42857142857143</v>
       </c>
       <c r="F22">
         <f>(2*(1-C22)+6*C22)*D22*1000000000</f>
-        <v>2.328266667e+11</v>
+        <v>232826666666.6667</v>
       </c>
       <c r="G22">
         <f>B22*1000000000000*F22</f>
-        <v>4.27782799e+27</v>
+        <v>4.2778279895023995e+27</v>
       </c>
       <c r="H22">
         <f>(G22/E22)/($G$8/$E$8)*$B$3</f>
-        <v>653.4271742</v>
+        <v>653.4271742029924</v>
       </c>
       <c r="I22">
         <f>MAX(H22,I21*(1-$B$5))</f>
-        <v>707.9920135</v>
+        <v>707.9920134743508</v>
       </c>
     </row>
     <row r="23">
@@ -18448,32 +18449,32 @@
       </c>
       <c r="B23">
         <f>'Efficiency Overlay'!R5+'Efficiency Overlay'!R7*$B$4</f>
-        <v>20019.81107</v>
+        <v>20019.811067386545</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D23">
-        <v>103.5</v>
+        <v>103.50000000000001</v>
       </c>
       <c r="E23">
-        <v>54.28571429</v>
+        <v>54.285714285714285</v>
       </c>
       <c r="F23">
         <f>(2*(1-C23)+6*C23)*D23*1000000000</f>
-        <v>2.07e+11</v>
+        <v>207000000000.00003</v>
       </c>
       <c r="G23">
         <f>B23*1000000000000*F23</f>
-        <v>4.144100891e+27</v>
+        <v>4.1441008909490154e+27</v>
       </c>
       <c r="H23">
         <f>(G23/E23)/($G$8/$E$8)*$B$3</f>
-        <v>599.6848788</v>
+        <v>599.684878766789</v>
       </c>
       <c r="I23">
         <f>MAX(H23,I22*(1-$B$5))</f>
-        <v>707.9920135</v>
+        <v>707.9920134743508</v>
       </c>
     </row>
     <row r="24">
@@ -18482,32 +18483,32 @@
       </c>
       <c r="B24">
         <f>'Efficiency Overlay'!S5+'Efficiency Overlay'!S7*$B$4</f>
-        <v>21860.12394</v>
+        <v>21860.123936624695</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D24">
-        <v>103.5</v>
+        <v>103.50000000000001</v>
       </c>
       <c r="E24">
-        <v>57.14285714</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="F24">
         <f>(2*(1-C24)+6*C24)*D24*1000000000</f>
-        <v>2.07e+11</v>
+        <v>207000000000.00003</v>
       </c>
       <c r="G24">
         <f>B24*1000000000000*F24</f>
-        <v>4.525045655e+27</v>
+        <v>4.525045654881313e+27</v>
       </c>
       <c r="H24">
         <f>(G24/E24)/($G$8/$E$8)*$B$3</f>
-        <v>622.0701305</v>
+        <v>622.0701305424171</v>
       </c>
       <c r="I24">
         <f>MAX(H24,I23*(1-$B$5))</f>
-        <v>707.9920135</v>
+        <v>707.9920134743508</v>
       </c>
     </row>
     <row r="25">
@@ -18516,32 +18517,32 @@
       </c>
       <c r="B25">
         <f>'Efficiency Overlay'!T5+'Efficiency Overlay'!T7*$B$4</f>
-        <v>23789.68866</v>
+        <v>23789.688660175238</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D25">
-        <v>103.5</v>
+        <v>103.50000000000001</v>
       </c>
       <c r="E25">
-        <v>60</v>
+        <v>60.0</v>
       </c>
       <c r="F25">
         <f>(2*(1-C25)+6*C25)*D25*1000000000</f>
-        <v>2.07e+11</v>
+        <v>207000000000.00003</v>
       </c>
       <c r="G25">
         <f>B25*1000000000000*F25</f>
-        <v>4.924465553e+27</v>
+        <v>4.9244655526562744e+27</v>
       </c>
       <c r="H25">
         <f>(G25/E25)/($G$8/$E$8)*$B$3</f>
-        <v>644.7423355</v>
+        <v>644.7423355487456</v>
       </c>
       <c r="I25">
         <f>MAX(H25,I24*(1-$B$5))</f>
-        <v>707.9920135</v>
+        <v>707.9920134743508</v>
       </c>
     </row>
   </sheetData>
@@ -19121,4 +19122,1108 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40"/>
+    <col min="2" max="10" width="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>OPERATING MODEL  —  Demand / Supply / Gap  (Bull / Base / Bear)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Set scenario in B3 (1=Bull, 2=Base, 3=Bear). Everything recomputes. Base inputs (tokens, N, TFLOP/W, training) live on 'FLOPs to Power'; this sheet overlays the scenario and adds supply + gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="47" t="inlineStr">
+        <is>
+          <t>SCENARIO  (1=Bull  2=Base  3=Bear)</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>active scenario</t>
+        </is>
+      </c>
+      <c r="B4" t="str">
+        <f>CHOOSE(B3,"Bull","Base","Bear")</f>
+        <v>Base</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="47" t="inlineStr">
+        <is>
+          <t>SCENARIO INPUTS</t>
+        </is>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D6" s="47" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>anchor GW 2025</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>70.0</v>
+      </c>
+      <c r="C7">
+        <v>70.0</v>
+      </c>
+      <c r="D7">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>token growth adj (per yr)</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.02</v>
+      </c>
+      <c r="C8">
+        <v>0.0</v>
+      </c>
+      <c r="D8">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>efficiency adj (per yr, + = faster = less power)</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>-0.015</v>
+      </c>
+      <c r="C9">
+        <v>0.0</v>
+      </c>
+      <c r="D9">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>capacity retirement (per yr)</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.0</v>
+      </c>
+      <c r="C10">
+        <v>0.0</v>
+      </c>
+      <c r="D10">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>supply build scale (x phase rates)</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.85</v>
+      </c>
+      <c r="C11">
+        <v>1.0</v>
+      </c>
+      <c r="D11">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="47" t="inlineStr">
+        <is>
+          <t>SUPPLY PHASE RATES (per yr, editable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2028-2030</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2031-2035</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2036-2042</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="47" t="inlineStr">
+        <is>
+          <t>ACTIVE (from scenario)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>anchor GW</t>
+        </is>
+      </c>
+      <c r="B20">
+        <f>CHOOSE($B$3,B7,C7,D7)</f>
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>token growth adj</t>
+        </is>
+      </c>
+      <c r="B21">
+        <f>CHOOSE($B$3,B8,C8,D8)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>efficiency adj</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>CHOOSE($B$3,B9,C9,D9)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>retirement rate</t>
+        </is>
+      </c>
+      <c r="B23">
+        <f>CHOOSE($B$3,B10,C10,D10)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>supply build scale</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>CHOOSE($B$3,B11,C11,D11)</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="47" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B27" s="47" t="inlineStr">
+        <is>
+          <t>tokens/day T</t>
+        </is>
+      </c>
+      <c r="C27" s="47" t="inlineStr">
+        <is>
+          <t>FLOPs/token</t>
+        </is>
+      </c>
+      <c r="D27" s="47" t="inlineStr">
+        <is>
+          <t>eff TFLOP/W</t>
+        </is>
+      </c>
+      <c r="E27" s="47" t="inlineStr">
+        <is>
+          <t>raw demand GW</t>
+        </is>
+      </c>
+      <c r="F27" s="47" t="inlineStr">
+        <is>
+          <t>demand floored GW</t>
+        </is>
+      </c>
+      <c r="G27" s="47" t="inlineStr">
+        <is>
+          <t>supply GW</t>
+        </is>
+      </c>
+      <c r="H27" s="47" t="inlineStr">
+        <is>
+          <t>GAP GW</t>
+        </is>
+      </c>
+      <c r="I27" s="47" t="inlineStr">
+        <is>
+          <t>_bal</t>
+        </is>
+      </c>
+      <c r="J27" s="47" t="inlineStr">
+        <is>
+          <t>_over</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>2025</v>
+      </c>
+      <c r="B28">
+        <f>'FLOPs to Power'!B8*(1+$B$21)^0</f>
+        <v>134.9222</v>
+      </c>
+      <c r="C28">
+        <f>'FLOPs to Power'!F8</f>
+        <v>594400000000.0</v>
+      </c>
+      <c r="D28">
+        <f>'FLOPs to Power'!E8*(1+$B$22)^0</f>
+        <v>9.0</v>
+      </c>
+      <c r="E28">
+        <f>(B28*C28/D28)/(B28*C28/D28)*$B$20</f>
+        <v>70.0</v>
+      </c>
+      <c r="F28">
+        <f>E28</f>
+        <v>70.0</v>
+      </c>
+      <c r="G28">
+        <f>$B$20</f>
+        <v>70.0</v>
+      </c>
+      <c r="H28">
+        <f>F28-G28</f>
+        <v>0.0</v>
+      </c>
+      <c r="I28">
+        <f>IF(AND(A28&gt;=$B$48,H28&lt;30),A28,99999)</f>
+        <v>99999</v>
+      </c>
+      <c r="J28">
+        <f>IF(H28&lt;0,A28,99999)</f>
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>2026</v>
+      </c>
+      <c r="B29">
+        <f>'FLOPs to Power'!B9*(1+$B$21)^1</f>
+        <v>460.844025</v>
+      </c>
+      <c r="C29">
+        <f>'FLOPs to Power'!F9</f>
+        <v>568573333333.3335</v>
+      </c>
+      <c r="D29">
+        <f>'FLOPs to Power'!E9*(1+$B$22)^1</f>
+        <v>11.0</v>
+      </c>
+      <c r="E29">
+        <f>(B29*C29/D29)/(B28*C28/D28)*$B$20</f>
+        <v>187.12253724689498</v>
+      </c>
+      <c r="F29">
+        <f>MAX(E29,F28*(1-$B$23))</f>
+        <v>187.12253724689498</v>
+      </c>
+      <c r="G29">
+        <f>G28*(1+IF(A29&lt;=2027,$B$14,IF(A29&lt;=2030,$B$15,IF(A29&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>85.39999999999999</v>
+      </c>
+      <c r="H29">
+        <f>F29-G29</f>
+        <v>101.72253724689499</v>
+      </c>
+      <c r="I29">
+        <f>IF(AND(A29&gt;=$B$48,H29&lt;30),A29,99999)</f>
+        <v>99999</v>
+      </c>
+      <c r="J29">
+        <f>IF(H29&lt;0,A29,99999)</f>
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>2027</v>
+      </c>
+      <c r="B30">
+        <f>'FLOPs to Power'!B10*(1+$B$21)^2</f>
+        <v>763.613276375</v>
+      </c>
+      <c r="C30">
+        <f>'FLOPs to Power'!F10</f>
+        <v>542746666666.6667</v>
+      </c>
+      <c r="D30">
+        <f>'FLOPs to Power'!E10*(1+$B$22)^2</f>
+        <v>14.0</v>
+      </c>
+      <c r="E30">
+        <f>(B30*C30/D30)/(B28*C28/D28)*$B$20</f>
+        <v>232.55245809233412</v>
+      </c>
+      <c r="F30">
+        <f>MAX(E30,F29*(1-$B$23))</f>
+        <v>232.55245809233412</v>
+      </c>
+      <c r="G30">
+        <f>G29*(1+IF(A30&lt;=2027,$B$14,IF(A30&lt;=2030,$B$15,IF(A30&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>104.18799999999999</v>
+      </c>
+      <c r="H30">
+        <f>F30-G30</f>
+        <v>128.36445809233413</v>
+      </c>
+      <c r="I30">
+        <f>IF(AND(A30&gt;=$B$48,H30&lt;30),A30,99999)</f>
+        <v>99999</v>
+      </c>
+      <c r="J30">
+        <f>IF(H30&lt;0,A30,99999)</f>
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>2028</v>
+      </c>
+      <c r="B31">
+        <f>'FLOPs to Power'!B11*(1+$B$21)^3</f>
+        <v>1359.8027322304688</v>
+      </c>
+      <c r="C31">
+        <f>'FLOPs to Power'!F11</f>
+        <v>516920000000.00006</v>
+      </c>
+      <c r="D31">
+        <f>'FLOPs to Power'!E11*(1+$B$22)^3</f>
+        <v>18.0</v>
+      </c>
+      <c r="E31">
+        <f>(B31*C31/D31)/(B28*C28/D28)*$B$20</f>
+        <v>306.76448216611846</v>
+      </c>
+      <c r="F31">
+        <f>MAX(E31,F30*(1-$B$23))</f>
+        <v>306.76448216611846</v>
+      </c>
+      <c r="G31">
+        <f>G30*(1+IF(A31&lt;=2027,$B$14,IF(A31&lt;=2030,$B$15,IF(A31&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>135.4444</v>
+      </c>
+      <c r="H31">
+        <f>F31-G31</f>
+        <v>171.32008216611845</v>
+      </c>
+      <c r="I31">
+        <f>IF(AND(A31&gt;=$B$48,H31&lt;30),A31,99999)</f>
+        <v>99999</v>
+      </c>
+      <c r="J31">
+        <f>IF(H31&lt;0,A31,99999)</f>
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>2029</v>
+      </c>
+      <c r="B32">
+        <f>'FLOPs to Power'!B12*(1+$B$21)^4</f>
+        <v>2172.793753804055</v>
+      </c>
+      <c r="C32">
+        <f>'FLOPs to Power'!F12</f>
+        <v>491093333333.3334</v>
+      </c>
+      <c r="D32">
+        <f>'FLOPs to Power'!E12*(1+$B$22)^4</f>
+        <v>21.5</v>
+      </c>
+      <c r="E32">
+        <f>(B32*C32/D32)/(B28*C28/D28)*$B$20</f>
+        <v>389.8723334685694</v>
+      </c>
+      <c r="F32">
+        <f>MAX(E32,F31*(1-$B$23))</f>
+        <v>389.8723334685694</v>
+      </c>
+      <c r="G32">
+        <f>G31*(1+IF(A32&lt;=2027,$B$14,IF(A32&lt;=2030,$B$15,IF(A32&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>176.07772</v>
+      </c>
+      <c r="H32">
+        <f>F32-G32</f>
+        <v>213.79461346856942</v>
+      </c>
+      <c r="I32">
+        <f>IF(AND(A32&gt;=$B$48,H32&lt;30),A32,99999)</f>
+        <v>99999</v>
+      </c>
+      <c r="J32">
+        <f>IF(H32&lt;0,A32,99999)</f>
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>2030</v>
+      </c>
+      <c r="B33">
+        <f>'FLOPs to Power'!B13*(1+$B$21)^5</f>
+        <v>3253.5840749501463</v>
+      </c>
+      <c r="C33">
+        <f>'FLOPs to Power'!F13</f>
+        <v>465266666666.66675</v>
+      </c>
+      <c r="D33">
+        <f>'FLOPs to Power'!E13*(1+$B$22)^5</f>
+        <v>25.0</v>
+      </c>
+      <c r="E33">
+        <f>(B33*C33/D33)/(B28*C28/D28)*$B$20</f>
+        <v>475.6662072622415</v>
+      </c>
+      <c r="F33">
+        <f>MAX(E33,F32*(1-$B$23))</f>
+        <v>475.6662072622415</v>
+      </c>
+      <c r="G33">
+        <f>G32*(1+IF(A33&lt;=2027,$B$14,IF(A33&lt;=2030,$B$15,IF(A33&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>228.901036</v>
+      </c>
+      <c r="H33">
+        <f>F33-G33</f>
+        <v>246.76517126224152</v>
+      </c>
+      <c r="I33">
+        <f>IF(AND(A33&gt;=$B$48,H33&lt;30),A33,99999)</f>
+        <v>99999</v>
+      </c>
+      <c r="J33">
+        <f>IF(H33&lt;0,A33,99999)</f>
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>2031</v>
+      </c>
+      <c r="B34">
+        <f>'FLOPs to Power'!B14*(1+$B$21)^6</f>
+        <v>4573.0374147267485</v>
+      </c>
+      <c r="C34">
+        <f>'FLOPs to Power'!F14</f>
+        <v>439440000000.0</v>
+      </c>
+      <c r="D34">
+        <f>'FLOPs to Power'!E14*(1+$B$22)^6</f>
+        <v>28.0</v>
+      </c>
+      <c r="E34">
+        <f>(B34*C34/D34)/(B28*C28/D28)*$B$20</f>
+        <v>563.7994448970002</v>
+      </c>
+      <c r="F34">
+        <f>MAX(E34,F33*(1-$B$23))</f>
+        <v>563.7994448970002</v>
+      </c>
+      <c r="G34">
+        <f>G33*(1+IF(A34&lt;=2027,$B$14,IF(A34&lt;=2030,$B$15,IF(A34&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>286.126295</v>
+      </c>
+      <c r="H34">
+        <f>F34-G34</f>
+        <v>277.67314989700014</v>
+      </c>
+      <c r="I34">
+        <f>IF(AND(A34&gt;=$B$48,H34&lt;30),A34,99999)</f>
+        <v>99999</v>
+      </c>
+      <c r="J34">
+        <f>IF(H34&lt;0,A34,99999)</f>
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>2032</v>
+      </c>
+      <c r="B35">
+        <f>'FLOPs to Power'!B15*(1+$B$21)^7</f>
+        <v>5901.417521751226</v>
+      </c>
+      <c r="C35">
+        <f>'FLOPs to Power'!F15</f>
+        <v>413613333333.3334</v>
+      </c>
+      <c r="D35">
+        <f>'FLOPs to Power'!E15*(1+$B$22)^7</f>
+        <v>31.0</v>
+      </c>
+      <c r="E35">
+        <f>(B35*C35/D35)/(B28*C28/D28)*$B$20</f>
+        <v>618.5396053977472</v>
+      </c>
+      <c r="F35">
+        <f>MAX(E35,F34*(1-$B$23))</f>
+        <v>618.5396053977472</v>
+      </c>
+      <c r="G35">
+        <f>G34*(1+IF(A35&lt;=2027,$B$14,IF(A35&lt;=2030,$B$15,IF(A35&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>357.65786875000003</v>
+      </c>
+      <c r="H35">
+        <f>F35-G35</f>
+        <v>260.8817366477472</v>
+      </c>
+      <c r="I35">
+        <f>IF(AND(A35&gt;=$B$48,H35&lt;30),A35,99999)</f>
+        <v>99999</v>
+      </c>
+      <c r="J35">
+        <f>IF(H35&lt;0,A35,99999)</f>
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>2033</v>
+      </c>
+      <c r="B36">
+        <f>'FLOPs to Power'!B16*(1+$B$21)^8</f>
+        <v>7334.615906104267</v>
+      </c>
+      <c r="C36">
+        <f>'FLOPs to Power'!F16</f>
+        <v>387786666666.6667</v>
+      </c>
+      <c r="D36">
+        <f>'FLOPs to Power'!E16*(1+$B$22)^8</f>
+        <v>34.0</v>
+      </c>
+      <c r="E36">
+        <f>(B36*C36/D36)/(B28*C28/D28)*$B$20</f>
+        <v>657.1577986546977</v>
+      </c>
+      <c r="F36">
+        <f>MAX(E36,F35*(1-$B$23))</f>
+        <v>657.1577986546977</v>
+      </c>
+      <c r="G36">
+        <f>G35*(1+IF(A36&lt;=2027,$B$14,IF(A36&lt;=2030,$B$15,IF(A36&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>447.07233593750004</v>
+      </c>
+      <c r="H36">
+        <f>F36-G36</f>
+        <v>210.08546271719763</v>
+      </c>
+      <c r="I36">
+        <f>IF(AND(A36&gt;=$B$48,H36&lt;30),A36,99999)</f>
+        <v>99999</v>
+      </c>
+      <c r="J36">
+        <f>IF(H36&lt;0,A36,99999)</f>
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>2034</v>
+      </c>
+      <c r="B37">
+        <f>'FLOPs to Power'!B17*(1+$B$21)^9</f>
+        <v>8998.706093065295</v>
+      </c>
+      <c r="C37">
+        <f>'FLOPs to Power'!F17</f>
+        <v>361960000000.00006</v>
+      </c>
+      <c r="D37">
+        <f>'FLOPs to Power'!E17*(1+$B$22)^9</f>
+        <v>37.0</v>
+      </c>
+      <c r="E37">
+        <f>(B37*C37/D37)/(B28*C28/D28)*$B$20</f>
+        <v>691.5399236892711</v>
+      </c>
+      <c r="F37">
+        <f>MAX(E37,F36*(1-$B$23))</f>
+        <v>691.5399236892711</v>
+      </c>
+      <c r="G37">
+        <f>G36*(1+IF(A37&lt;=2027,$B$14,IF(A37&lt;=2030,$B$15,IF(A37&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>558.8404199218751</v>
+      </c>
+      <c r="H37">
+        <f>F37-G37</f>
+        <v>132.69950376739598</v>
+      </c>
+      <c r="I37">
+        <f>IF(AND(A37&gt;=$B$48,H37&lt;30),A37,99999)</f>
+        <v>99999</v>
+      </c>
+      <c r="J37">
+        <f>IF(H37&lt;0,A37,99999)</f>
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>2035</v>
+      </c>
+      <c r="B38">
+        <f>'FLOPs to Power'!B18*(1+$B$21)^10</f>
+        <v>10620.445661620677</v>
+      </c>
+      <c r="C38">
+        <f>'FLOPs to Power'!F18</f>
+        <v>336133333333.3334</v>
+      </c>
+      <c r="D38">
+        <f>'FLOPs to Power'!E18*(1+$B$22)^10</f>
+        <v>40.0</v>
+      </c>
+      <c r="E38">
+        <f>(B38*C38/D38)/(B28*C28/D28)*$B$20</f>
+        <v>701.088215006094</v>
+      </c>
+      <c r="F38">
+        <f>MAX(E38,F37*(1-$B$23))</f>
+        <v>701.088215006094</v>
+      </c>
+      <c r="G38">
+        <f>G37*(1+IF(A38&lt;=2027,$B$14,IF(A38&lt;=2030,$B$15,IF(A38&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>698.5505249023438</v>
+      </c>
+      <c r="H38">
+        <f>F38-G38</f>
+        <v>2.537690103750151</v>
+      </c>
+      <c r="I38">
+        <f>IF(AND(A38&gt;=$B$48,H38&lt;30),A38,99999)</f>
+        <v>2035</v>
+      </c>
+      <c r="J38">
+        <f>IF(H38&lt;0,A38,99999)</f>
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>2036</v>
+      </c>
+      <c r="B39">
+        <f>'FLOPs to Power'!B19*(1+$B$21)^11</f>
+        <v>12433.27320756883</v>
+      </c>
+      <c r="C39">
+        <f>'FLOPs to Power'!F19</f>
+        <v>310306666666.6667</v>
+      </c>
+      <c r="D39">
+        <f>'FLOPs to Power'!E19*(1+$B$22)^11</f>
+        <v>42.857142857142854</v>
+      </c>
+      <c r="E39">
+        <f>(B39*C39/D39)/(B28*C28/D28)*$B$20</f>
+        <v>707.1828222825758</v>
+      </c>
+      <c r="F39">
+        <f>MAX(E39,F38*(1-$B$23))</f>
+        <v>707.1828222825758</v>
+      </c>
+      <c r="G39">
+        <f>G38*(1+IF(A39&lt;=2027,$B$14,IF(A39&lt;=2030,$B$15,IF(A39&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>803.3331036376953</v>
+      </c>
+      <c r="H39">
+        <f>F39-G39</f>
+        <v>-96.15028135511955</v>
+      </c>
+      <c r="I39">
+        <f>IF(AND(A39&gt;=$B$48,H39&lt;30),A39,99999)</f>
+        <v>2036</v>
+      </c>
+      <c r="J39">
+        <f>IF(H39&lt;0,A39,99999)</f>
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>2037</v>
+      </c>
+      <c r="B40">
+        <f>'FLOPs to Power'!B20*(1+$B$21)^12</f>
+        <v>14482.722955550775</v>
+      </c>
+      <c r="C40">
+        <f>'FLOPs to Power'!F20</f>
+        <v>284480000000.0</v>
+      </c>
+      <c r="D40">
+        <f>'FLOPs to Power'!E20*(1+$B$22)^12</f>
+        <v>45.714285714285715</v>
+      </c>
+      <c r="E40">
+        <f>(B40*C40/D40)/(B28*C28/D28)*$B$20</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="F40">
+        <f>MAX(E40,F39*(1-$B$23))</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="G40">
+        <f>G39*(1+IF(A40&lt;=2027,$B$14,IF(A40&lt;=2030,$B$15,IF(A40&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>923.8330691833496</v>
+      </c>
+      <c r="H40">
+        <f>F40-G40</f>
+        <v>-215.84105570899885</v>
+      </c>
+      <c r="I40">
+        <f>IF(AND(A40&gt;=$B$48,H40&lt;30),A40,99999)</f>
+        <v>2037</v>
+      </c>
+      <c r="J40">
+        <f>IF(H40&lt;0,A40,99999)</f>
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>2038</v>
+      </c>
+      <c r="B41">
+        <f>'FLOPs to Power'!B21*(1+$B$21)^13</f>
+        <v>16709.132646039423</v>
+      </c>
+      <c r="C41">
+        <f>'FLOPs to Power'!F21</f>
+        <v>258653333333.33337</v>
+      </c>
+      <c r="D41">
+        <f>'FLOPs to Power'!E21*(1+$B$22)^13</f>
+        <v>48.57142857142857</v>
+      </c>
+      <c r="E41">
+        <f>(B41*C41/D41)/(B28*C28/D28)*$B$20</f>
+        <v>698.9875557644822</v>
+      </c>
+      <c r="F41">
+        <f>MAX(E41,F40*(1-$B$23))</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="G41">
+        <f>G40*(1+IF(A41&lt;=2027,$B$14,IF(A41&lt;=2030,$B$15,IF(A41&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>1062.408029560852</v>
+      </c>
+      <c r="H41">
+        <f>F41-G41</f>
+        <v>-354.41601608650114</v>
+      </c>
+      <c r="I41">
+        <f>IF(AND(A41&gt;=$B$48,H41&lt;30),A41,99999)</f>
+        <v>2038</v>
+      </c>
+      <c r="J41">
+        <f>IF(H41&lt;0,A41,99999)</f>
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>2039</v>
+      </c>
+      <c r="B42">
+        <f>'FLOPs to Power'!B22*(1+$B$21)^14</f>
+        <v>18373.445150193562</v>
+      </c>
+      <c r="C42">
+        <f>'FLOPs to Power'!F22</f>
+        <v>232826666666.6667</v>
+      </c>
+      <c r="D42">
+        <f>'FLOPs to Power'!E22*(1+$B$22)^14</f>
+        <v>51.42857142857143</v>
+      </c>
+      <c r="E42">
+        <f>(B42*C42/D42)/(B28*C28/D28)*$B$20</f>
+        <v>653.4271742029925</v>
+      </c>
+      <c r="F42">
+        <f>MAX(E42,F41*(1-$B$23))</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="G42">
+        <f>G41*(1+IF(A42&lt;=2027,$B$14,IF(A42&lt;=2030,$B$15,IF(A42&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>1221.7692339949797</v>
+      </c>
+      <c r="H42">
+        <f>F42-G42</f>
+        <v>-513.7772205206289</v>
+      </c>
+      <c r="I42">
+        <f>IF(AND(A42&gt;=$B$48,H42&lt;30),A42,99999)</f>
+        <v>2039</v>
+      </c>
+      <c r="J42">
+        <f>IF(H42&lt;0,A42,99999)</f>
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>2040</v>
+      </c>
+      <c r="B43">
+        <f>'FLOPs to Power'!B23*(1+$B$21)^15</f>
+        <v>20019.811067386545</v>
+      </c>
+      <c r="C43">
+        <f>'FLOPs to Power'!F23</f>
+        <v>207000000000.00003</v>
+      </c>
+      <c r="D43">
+        <f>'FLOPs to Power'!E23*(1+$B$22)^15</f>
+        <v>54.285714285714285</v>
+      </c>
+      <c r="E43">
+        <f>(B43*C43/D43)/(B28*C28/D28)*$B$20</f>
+        <v>599.684878766789</v>
+      </c>
+      <c r="F43">
+        <f>MAX(E43,F42*(1-$B$23))</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="G43">
+        <f>G42*(1+IF(A43&lt;=2027,$B$14,IF(A43&lt;=2030,$B$15,IF(A43&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>1405.0346190942266</v>
+      </c>
+      <c r="H43">
+        <f>F43-G43</f>
+        <v>-697.0426056198759</v>
+      </c>
+      <c r="I43">
+        <f>IF(AND(A43&gt;=$B$48,H43&lt;30),A43,99999)</f>
+        <v>2040</v>
+      </c>
+      <c r="J43">
+        <f>IF(H43&lt;0,A43,99999)</f>
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>2041</v>
+      </c>
+      <c r="B44">
+        <f>'FLOPs to Power'!B24*(1+$B$21)^16</f>
+        <v>21860.123936624695</v>
+      </c>
+      <c r="C44">
+        <f>'FLOPs to Power'!F24</f>
+        <v>207000000000.00003</v>
+      </c>
+      <c r="D44">
+        <f>'FLOPs to Power'!E24*(1+$B$22)^16</f>
+        <v>57.14285714285714</v>
+      </c>
+      <c r="E44">
+        <f>(B44*C44/D44)/(B28*C28/D28)*$B$20</f>
+        <v>622.0701305424171</v>
+      </c>
+      <c r="F44">
+        <f>MAX(E44,F43*(1-$B$23))</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="G44">
+        <f>G43*(1+IF(A44&lt;=2027,$B$14,IF(A44&lt;=2030,$B$15,IF(A44&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>1615.7898119583606</v>
+      </c>
+      <c r="H44">
+        <f>F44-G44</f>
+        <v>-907.7977984840098</v>
+      </c>
+      <c r="I44">
+        <f>IF(AND(A44&gt;=$B$48,H44&lt;30),A44,99999)</f>
+        <v>2041</v>
+      </c>
+      <c r="J44">
+        <f>IF(H44&lt;0,A44,99999)</f>
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>2042</v>
+      </c>
+      <c r="B45">
+        <f>'FLOPs to Power'!B25*(1+$B$21)^17</f>
+        <v>23789.688660175238</v>
+      </c>
+      <c r="C45">
+        <f>'FLOPs to Power'!F25</f>
+        <v>207000000000.00003</v>
+      </c>
+      <c r="D45">
+        <f>'FLOPs to Power'!E25*(1+$B$22)^17</f>
+        <v>60.0</v>
+      </c>
+      <c r="E45">
+        <f>(B45*C45/D45)/(B28*C28/D28)*$B$20</f>
+        <v>644.7423355487456</v>
+      </c>
+      <c r="F45">
+        <f>MAX(E45,F44*(1-$B$23))</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="G45">
+        <f>G44*(1+IF(A45&lt;=2027,$B$14,IF(A45&lt;=2030,$B$15,IF(A45&lt;=2035,$B$16,$B$17)))*$B$24)</f>
+        <v>1858.1582837521146</v>
+      </c>
+      <c r="H45">
+        <f>F45-G45</f>
+        <v>-1150.166270277764</v>
+      </c>
+      <c r="I45">
+        <f>IF(AND(A45&gt;=$B$48,H45&lt;30),A45,99999)</f>
+        <v>2042</v>
+      </c>
+      <c r="J45">
+        <f>IF(H45&lt;0,A45,99999)</f>
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="47" t="inlineStr">
+        <is>
+          <t>PEAK GAP (GW)</t>
+        </is>
+      </c>
+      <c r="B47">
+        <f>MAX(H28:H45)</f>
+        <v>277.67314989700014</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>peak year</t>
+        </is>
+      </c>
+      <c r="B48">
+        <f>INDEX(A28:A45,MATCH(MAX(H28:H45),H28:H45,0))</f>
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>balance year (gap&lt;30 after peak)</t>
+        </is>
+      </c>
+      <c r="B49">
+        <f>IF(MIN(I28:I45)=99999,"post-2042",MIN(I28:I45))</f>
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>overshoot year (gap&lt;0)</t>
+        </is>
+      </c>
+      <c r="B50">
+        <f>IF(MIN(J28:J45)=99999,"post-2042",MIN(J28:J45))</f>
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>demand floor 2042 (GW)</t>
+        </is>
+      </c>
+      <c r="B51">
+        <f>ROUND(F45,0)</f>
+        <v>708</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/Token_and_Data_Build_Out_v4_2.xlsx
+++ b/Token_and_Data_Build_Out_v4_2.xlsx
@@ -19322,31 +19322,31 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40"/>
-    <col min="2" max="13" width="15"/>
+    <col min="1" max="1" width="46"/>
+    <col min="2" max="14" width="15"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="47" t="inlineStr">
         <is>
-          <t>OPERATING MODEL  —  Demand / Supply / Gap  (Bull / Base / Bear)</t>
+          <t>OPERATING MODEL  —  Demand / Supply / Gap  (Bull / Base / Bear / Central)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Set scenario in B3 (1=Bull, 2=Base, 3=Bear). Everything recomputes. Base inputs (tokens, N, TFLOP/W, training) live on 'FLOPs to Power'; this sheet overlays the scenario and adds supply + gap. ITEM 10: a shortage utilization ceiling (Bear=40%) crams the fleet in short years.</t>
+          <t>Set scenario in B3 (1=Bull, 2=Base, 3=Bear, 4=Central). Everything recomputes. CENTRAL = most-likely COUPLED case: second-wave agentic demand 10%/yr from 2034 AND STRUCTURAL utilization ramping 2030-&gt;2040 toward 70% (batch ceiling). Util rises WITH agentic, always-on, so the demand surge is largely absorbed: realized power flattens mid-decade, then gently resumes once the ~25%-&gt;70% utilization runway is spent.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="47" t="inlineStr">
         <is>
-          <t>SCENARIO  (1=Bull  2=Base  3=Bear)</t>
+          <t>SCENARIO  (1=Bull 2=Base 3=Bear 4=Central)</t>
         </is>
       </c>
       <c r="B3">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="B4" t="str">
-        <f>CHOOSE(B3,"Bull","Base","Bear")</f>
+        <f>CHOOSE(B3,"Bull","Base","Bear","Central")</f>
         <v>Base</v>
       </c>
     </row>
@@ -19385,6 +19385,11 @@
           <t>Bear</t>
         </is>
       </c>
+      <c r="E6" s="47" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19401,6 +19406,9 @@
       <c r="D7">
         <v>70.0</v>
       </c>
+      <c r="E7">
+        <v>70.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19417,6 +19425,9 @@
       <c r="D8">
         <v>-0.02</v>
       </c>
+      <c r="E8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19433,6 +19444,9 @@
       <c r="D9">
         <v>0.03</v>
       </c>
+      <c r="E9">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19449,6 +19463,9 @@
       <c r="D10">
         <v>0.08</v>
       </c>
+      <c r="E10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19465,11 +19482,14 @@
       <c r="D11">
         <v>1.15</v>
       </c>
+      <c r="E11">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>shortage util ceiling (ITEM 10; 0 = off)</t>
+          <t>STRUCTURAL util ceiling (&lt;=0.25 = off; agentic batch ceiling)</t>
         </is>
       </c>
       <c r="B12">
@@ -19479,1131 +19499,982 @@
         <v>0.0</v>
       </c>
       <c r="D12">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="47" t="inlineStr">
+        <v>0.6</v>
+      </c>
+      <c r="E12">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ITEM7 second-wave demand re-accel /yr (0 = off)</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.0</v>
+      </c>
+      <c r="C13">
+        <v>0.0</v>
+      </c>
+      <c r="D13">
+        <v>0.0</v>
+      </c>
+      <c r="E13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="47" t="inlineStr">
         <is>
           <t>SUPPLY PHASE RATES (per yr, editable)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-2027</t>
         </is>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>0.22</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2028-2030</t>
         </is>
       </c>
-      <c r="B16">
+      <c r="B17">
         <v>0.3</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2031-2035</t>
         </is>
       </c>
-      <c r="B17">
+      <c r="B18">
         <v>0.25</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2036-2042</t>
         </is>
       </c>
-      <c r="B18">
+      <c r="B19">
         <v>0.15</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="47" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>second-wave start year (ITEM7)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>structural util ramp start year</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>structural util full year (hits ceiling)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="47" t="inlineStr">
         <is>
           <t>ACTIVE (from scenario)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>anchor GW</t>
         </is>
       </c>
-      <c r="B21">
-        <f>CHOOSE($B$3,B7,C7,D7)</f>
+      <c r="B26">
+        <f>CHOOSE($B$3,B7,C7,D7,E7)</f>
         <v>70.0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>token growth adj</t>
         </is>
       </c>
-      <c r="B22">
-        <f>CHOOSE($B$3,B8,C8,D8)</f>
+      <c r="B27">
+        <f>CHOOSE($B$3,B8,C8,D8,E8)</f>
         <v>0.0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>efficiency adj</t>
         </is>
       </c>
-      <c r="B23">
-        <f>CHOOSE($B$3,B9,C9,D9)</f>
+      <c r="B28">
+        <f>CHOOSE($B$3,B9,C9,D9,E9)</f>
         <v>0.0</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>retirement rate</t>
         </is>
       </c>
-      <c r="B24">
-        <f>CHOOSE($B$3,B10,C10,D10)</f>
+      <c r="B29">
+        <f>CHOOSE($B$3,B10,C10,D10,E10)</f>
         <v>0.0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>supply build scale</t>
         </is>
       </c>
-      <c r="B25">
-        <f>CHOOSE($B$3,B11,C11,D11)</f>
+      <c r="B30">
+        <f>CHOOSE($B$3,B11,C11,D11,E11)</f>
         <v>1.0</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
-          <t>shortage util ceiling</t>
+          <t>structural util ceiling</t>
         </is>
       </c>
-      <c r="B26">
-        <f>CHOOSE($B$3,B12,C12,D12)</f>
+      <c r="B31">
+        <f>CHOOSE($B$3,B12,C12,D12,E12)</f>
         <v>0.0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="47" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>second-wave growth</t>
+        </is>
+      </c>
+      <c r="B32">
+        <f>CHOOSE($B$3,B13,C13,D13,E13)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="47" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B29" s="47" t="inlineStr">
+      <c r="B34" s="47" t="inlineStr">
         <is>
           <t>tokens/day T</t>
         </is>
       </c>
-      <c r="C29" s="47" t="inlineStr">
+      <c r="C34" s="47" t="inlineStr">
         <is>
           <t>FLOPs/token</t>
         </is>
       </c>
-      <c r="D29" s="47" t="inlineStr">
+      <c r="D34" s="47" t="inlineStr">
         <is>
           <t>eff TFLOP/W</t>
         </is>
       </c>
-      <c r="E29" s="47" t="inlineStr">
+      <c r="E34" s="47" t="inlineStr">
         <is>
           <t>raw demand GW</t>
         </is>
       </c>
-      <c r="F29" s="47" t="inlineStr">
+      <c r="F34" s="47" t="inlineStr">
         <is>
           <t>demand floored GW</t>
         </is>
       </c>
-      <c r="G29" s="47" t="inlineStr">
+      <c r="G34" s="47" t="inlineStr">
         <is>
           <t>supply GW</t>
         </is>
       </c>
-      <c r="H29" s="47" t="inlineStr">
+      <c r="H34" s="47" t="inlineStr">
         <is>
           <t>base util</t>
         </is>
       </c>
-      <c r="I29" s="47" t="inlineStr">
+      <c r="I34" s="47" t="inlineStr">
         <is>
-          <t>util applied</t>
+          <t>util structural</t>
         </is>
       </c>
-      <c r="J29" s="47" t="inlineStr">
+      <c r="J34" s="47" t="inlineStr">
         <is>
-          <t>demand crammed GW</t>
+          <t>realized power GW</t>
         </is>
       </c>
-      <c r="K29" s="47" t="inlineStr">
+      <c r="K34" s="47" t="inlineStr">
         <is>
           <t>GAP GW</t>
         </is>
       </c>
-      <c r="L29" s="47" t="inlineStr">
+      <c r="L34" s="47" t="inlineStr">
         <is>
           <t>_bal</t>
         </is>
       </c>
-      <c r="M29" s="47" t="inlineStr">
+      <c r="M34" s="47" t="inlineStr">
         <is>
           <t>_over</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30">
+      <c r="N34" s="47" t="inlineStr">
+        <is>
+          <t>_asym</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
         <v>2025</v>
       </c>
-      <c r="B30">
-        <f>'FLOPs to Power'!B8*(1+$B$22)^0</f>
+      <c r="B35">
+        <f>'FLOPs to Power'!B8*(1+$B$27)^0</f>
         <v>134.9222</v>
       </c>
-      <c r="C30">
+      <c r="C35">
         <f>'FLOPs to Power'!F8</f>
         <v>594400000000.0</v>
       </c>
-      <c r="D30">
-        <f>'FLOPs to Power'!E8*(1+$B$23)^0</f>
+      <c r="D35">
+        <f>'FLOPs to Power'!E8*(1+$B$28)^0</f>
         <v>9.0</v>
       </c>
-      <c r="E30">
-        <f>(B30*C30/D30)/(B30*C30/D30)*$B$21</f>
+      <c r="E35">
+        <f>(B35*C35/D35)/(B35*C35/D35)*$B$26</f>
         <v>70.0</v>
       </c>
-      <c r="F30">
-        <f>E30</f>
+      <c r="F35">
+        <f>E35</f>
         <v>70.0</v>
       </c>
-      <c r="G30">
-        <f>$B$21</f>
+      <c r="G35">
+        <f>$B$26</f>
         <v>70.0</v>
-      </c>
-      <c r="H30">
-        <f>0.12+MIN(1,(A30-2025)/10)*(0.25-0.12)</f>
-        <v>0.12</v>
-      </c>
-      <c r="I30">
-        <f>IF(AND($B$26&gt;0,F30-G30&gt;0),MAX(H30,$B$26),H30)</f>
-        <v>0.12</v>
-      </c>
-      <c r="J30">
-        <f>F30*H30/I30</f>
-        <v>70.0</v>
-      </c>
-      <c r="K30">
-        <f>J30-G30</f>
-        <v>0.0</v>
-      </c>
-      <c r="L30">
-        <f>IF(AND(A30&gt;=$B$50,K30&lt;30),A30,99999)</f>
-        <v>99999</v>
-      </c>
-      <c r="M30">
-        <f>IF(K30&lt;0,A30,99999)</f>
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>2026</v>
-      </c>
-      <c r="B31">
-        <f>'FLOPs to Power'!B9*(1+$B$22)^1</f>
-        <v>460.844025</v>
-      </c>
-      <c r="C31">
-        <f>'FLOPs to Power'!F9</f>
-        <v>568573333333.3335</v>
-      </c>
-      <c r="D31">
-        <f>'FLOPs to Power'!E9*(1+$B$23)^1</f>
-        <v>11.0</v>
-      </c>
-      <c r="E31">
-        <f>(B31*C31/D31)/(B30*C30/D30)*$B$21</f>
-        <v>187.12253724689498</v>
-      </c>
-      <c r="F31">
-        <f>MAX(E31,F30*(1-$B$24))</f>
-        <v>187.12253724689498</v>
-      </c>
-      <c r="G31">
-        <f>G30*(1+IF(A31&lt;=2027,$B$15,IF(A31&lt;=2030,$B$16,IF(A31&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>85.39999999999999</v>
-      </c>
-      <c r="H31">
-        <f>0.12+MIN(1,(A31-2025)/10)*(0.25-0.12)</f>
-        <v>0.133</v>
-      </c>
-      <c r="I31">
-        <f>IF(AND($B$26&gt;0,F31-G31&gt;0),MAX(H31,$B$26),H31)</f>
-        <v>0.133</v>
-      </c>
-      <c r="J31">
-        <f>F31*H31/I31</f>
-        <v>187.12253724689498</v>
-      </c>
-      <c r="K31">
-        <f>J31-G31</f>
-        <v>101.72253724689499</v>
-      </c>
-      <c r="L31">
-        <f>IF(AND(A31&gt;=$B$50,K31&lt;30),A31,99999)</f>
-        <v>99999</v>
-      </c>
-      <c r="M31">
-        <f>IF(K31&lt;0,A31,99999)</f>
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>2027</v>
-      </c>
-      <c r="B32">
-        <f>'FLOPs to Power'!B10*(1+$B$22)^2</f>
-        <v>763.613276375</v>
-      </c>
-      <c r="C32">
-        <f>'FLOPs to Power'!F10</f>
-        <v>542746666666.6667</v>
-      </c>
-      <c r="D32">
-        <f>'FLOPs to Power'!E10*(1+$B$23)^2</f>
-        <v>14.0</v>
-      </c>
-      <c r="E32">
-        <f>(B32*C32/D32)/(B30*C30/D30)*$B$21</f>
-        <v>232.55245809233412</v>
-      </c>
-      <c r="F32">
-        <f>MAX(E32,F31*(1-$B$24))</f>
-        <v>232.55245809233412</v>
-      </c>
-      <c r="G32">
-        <f>G31*(1+IF(A32&lt;=2027,$B$15,IF(A32&lt;=2030,$B$16,IF(A32&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>104.18799999999999</v>
-      </c>
-      <c r="H32">
-        <f>0.12+MIN(1,(A32-2025)/10)*(0.25-0.12)</f>
-        <v>0.146</v>
-      </c>
-      <c r="I32">
-        <f>IF(AND($B$26&gt;0,F32-G32&gt;0),MAX(H32,$B$26),H32)</f>
-        <v>0.146</v>
-      </c>
-      <c r="J32">
-        <f>F32*H32/I32</f>
-        <v>232.55245809233412</v>
-      </c>
-      <c r="K32">
-        <f>J32-G32</f>
-        <v>128.36445809233413</v>
-      </c>
-      <c r="L32">
-        <f>IF(AND(A32&gt;=$B$50,K32&lt;30),A32,99999)</f>
-        <v>99999</v>
-      </c>
-      <c r="M32">
-        <f>IF(K32&lt;0,A32,99999)</f>
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>2028</v>
-      </c>
-      <c r="B33">
-        <f>'FLOPs to Power'!B11*(1+$B$22)^3</f>
-        <v>1359.8027322304688</v>
-      </c>
-      <c r="C33">
-        <f>'FLOPs to Power'!F11</f>
-        <v>516920000000.00006</v>
-      </c>
-      <c r="D33">
-        <f>'FLOPs to Power'!E11*(1+$B$23)^3</f>
-        <v>18.0</v>
-      </c>
-      <c r="E33">
-        <f>(B33*C33/D33)/(B30*C30/D30)*$B$21</f>
-        <v>306.76448216611846</v>
-      </c>
-      <c r="F33">
-        <f>MAX(E33,F32*(1-$B$24))</f>
-        <v>306.76448216611846</v>
-      </c>
-      <c r="G33">
-        <f>G32*(1+IF(A33&lt;=2027,$B$15,IF(A33&lt;=2030,$B$16,IF(A33&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>135.4444</v>
-      </c>
-      <c r="H33">
-        <f>0.12+MIN(1,(A33-2025)/10)*(0.25-0.12)</f>
-        <v>0.159</v>
-      </c>
-      <c r="I33">
-        <f>IF(AND($B$26&gt;0,F33-G33&gt;0),MAX(H33,$B$26),H33)</f>
-        <v>0.159</v>
-      </c>
-      <c r="J33">
-        <f>F33*H33/I33</f>
-        <v>306.76448216611846</v>
-      </c>
-      <c r="K33">
-        <f>J33-G33</f>
-        <v>171.32008216611845</v>
-      </c>
-      <c r="L33">
-        <f>IF(AND(A33&gt;=$B$50,K33&lt;30),A33,99999)</f>
-        <v>99999</v>
-      </c>
-      <c r="M33">
-        <f>IF(K33&lt;0,A33,99999)</f>
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>2029</v>
-      </c>
-      <c r="B34">
-        <f>'FLOPs to Power'!B12*(1+$B$22)^4</f>
-        <v>2172.793753804055</v>
-      </c>
-      <c r="C34">
-        <f>'FLOPs to Power'!F12</f>
-        <v>491093333333.3334</v>
-      </c>
-      <c r="D34">
-        <f>'FLOPs to Power'!E12*(1+$B$23)^4</f>
-        <v>21.5</v>
-      </c>
-      <c r="E34">
-        <f>(B34*C34/D34)/(B30*C30/D30)*$B$21</f>
-        <v>389.8723334685694</v>
-      </c>
-      <c r="F34">
-        <f>MAX(E34,F33*(1-$B$24))</f>
-        <v>389.8723334685694</v>
-      </c>
-      <c r="G34">
-        <f>G33*(1+IF(A34&lt;=2027,$B$15,IF(A34&lt;=2030,$B$16,IF(A34&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>176.07772</v>
-      </c>
-      <c r="H34">
-        <f>0.12+MIN(1,(A34-2025)/10)*(0.25-0.12)</f>
-        <v>0.172</v>
-      </c>
-      <c r="I34">
-        <f>IF(AND($B$26&gt;0,F34-G34&gt;0),MAX(H34,$B$26),H34)</f>
-        <v>0.172</v>
-      </c>
-      <c r="J34">
-        <f>F34*H34/I34</f>
-        <v>389.8723334685694</v>
-      </c>
-      <c r="K34">
-        <f>J34-G34</f>
-        <v>213.79461346856942</v>
-      </c>
-      <c r="L34">
-        <f>IF(AND(A34&gt;=$B$50,K34&lt;30),A34,99999)</f>
-        <v>99999</v>
-      </c>
-      <c r="M34">
-        <f>IF(K34&lt;0,A34,99999)</f>
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>2030</v>
-      </c>
-      <c r="B35">
-        <f>'FLOPs to Power'!B13*(1+$B$22)^5</f>
-        <v>3253.5840749501463</v>
-      </c>
-      <c r="C35">
-        <f>'FLOPs to Power'!F13</f>
-        <v>465266666666.66675</v>
-      </c>
-      <c r="D35">
-        <f>'FLOPs to Power'!E13*(1+$B$23)^5</f>
-        <v>25.0</v>
-      </c>
-      <c r="E35">
-        <f>(B35*C35/D35)/(B30*C30/D30)*$B$21</f>
-        <v>475.6662072622415</v>
-      </c>
-      <c r="F35">
-        <f>MAX(E35,F34*(1-$B$24))</f>
-        <v>475.6662072622415</v>
-      </c>
-      <c r="G35">
-        <f>G34*(1+IF(A35&lt;=2027,$B$15,IF(A35&lt;=2030,$B$16,IF(A35&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>228.901036</v>
       </c>
       <c r="H35">
         <f>0.12+MIN(1,(A35-2025)/10)*(0.25-0.12)</f>
-        <v>0.185</v>
+        <v>0.12</v>
       </c>
       <c r="I35">
-        <f>IF(AND($B$26&gt;0,F35-G35&gt;0),MAX(H35,$B$26),H35)</f>
-        <v>0.185</v>
+        <f>IF($B$31&lt;=0.25,H35,IF(A35&lt;=$B$22,H35,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A35-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
+        <v>0.12</v>
       </c>
       <c r="J35">
         <f>F35*H35/I35</f>
-        <v>475.66620726224147</v>
+        <v>70.0</v>
       </c>
       <c r="K35">
         <f>J35-G35</f>
-        <v>246.76517126224147</v>
+        <v>0.0</v>
       </c>
       <c r="L35">
-        <f>IF(AND(A35&gt;=$B$50,K35&lt;30),A35,99999)</f>
+        <f>IF(AND(A35&gt;=$B$55,K35&lt;30),A35,99999)</f>
         <v>99999</v>
       </c>
       <c r="M35">
         <f>IF(K35&lt;0,A35,99999)</f>
         <v>99999</v>
       </c>
+      <c r="N35">
+        <f>99999</f>
+        <v>99999</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>2031</v>
+        <v>2026</v>
       </c>
       <c r="B36">
-        <f>'FLOPs to Power'!B14*(1+$B$22)^6</f>
-        <v>4573.0374147267485</v>
+        <f>'FLOPs to Power'!B9*(1+$B$27)^1</f>
+        <v>460.844025</v>
       </c>
       <c r="C36">
-        <f>'FLOPs to Power'!F14</f>
-        <v>439440000000.0</v>
+        <f>'FLOPs to Power'!F9</f>
+        <v>568573333333.3335</v>
       </c>
       <c r="D36">
-        <f>'FLOPs to Power'!E14*(1+$B$23)^6</f>
-        <v>28.0</v>
+        <f>'FLOPs to Power'!E9*(1+$B$28)^1</f>
+        <v>11.0</v>
       </c>
       <c r="E36">
-        <f>(B36*C36/D36)/(B30*C30/D30)*$B$21</f>
-        <v>563.7994448970002</v>
+        <f>(B36*C36/D36)/(B35*C35/D35)*$B$26</f>
+        <v>187.12253724689498</v>
       </c>
       <c r="F36">
-        <f>MAX(E36,F35*(1-$B$24))</f>
-        <v>563.7994448970002</v>
+        <f>MAX(E36,F35*(1-$B$29),IF(A36&gt;=$B$21,F35*(1+MIN((B36-B35)/B35,$B$32)),0))</f>
+        <v>187.12253724689498</v>
       </c>
       <c r="G36">
-        <f>G35*(1+IF(A36&lt;=2027,$B$15,IF(A36&lt;=2030,$B$16,IF(A36&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>286.126295</v>
+        <f>G35*(1+IF(A36&lt;=2027,$B$16,IF(A36&lt;=2030,$B$17,IF(A36&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>85.39999999999999</v>
       </c>
       <c r="H36">
         <f>0.12+MIN(1,(A36-2025)/10)*(0.25-0.12)</f>
-        <v>0.198</v>
+        <v>0.133</v>
       </c>
       <c r="I36">
-        <f>IF(AND($B$26&gt;0,F36-G36&gt;0),MAX(H36,$B$26),H36)</f>
-        <v>0.198</v>
+        <f>IF($B$31&lt;=0.25,H36,IF(A36&lt;=$B$22,H36,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A36-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
+        <v>0.133</v>
       </c>
       <c r="J36">
         <f>F36*H36/I36</f>
-        <v>563.7994448970002</v>
+        <v>187.12253724689498</v>
       </c>
       <c r="K36">
         <f>J36-G36</f>
-        <v>277.67314989700014</v>
+        <v>101.72253724689499</v>
       </c>
       <c r="L36">
-        <f>IF(AND(A36&gt;=$B$50,K36&lt;30),A36,99999)</f>
+        <f>IF(AND(A36&gt;=$B$55,K36&lt;30),A36,99999)</f>
         <v>99999</v>
       </c>
       <c r="M36">
         <f>IF(K36&lt;0,A36,99999)</f>
         <v>99999</v>
       </c>
+      <c r="N36">
+        <f>IF(AND(A36&gt;2027,(J36-J35)/J35&lt;0.02),A36,99999)</f>
+        <v>99999</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>2032</v>
+        <v>2027</v>
       </c>
       <c r="B37">
-        <f>'FLOPs to Power'!B15*(1+$B$22)^7</f>
-        <v>5901.417521751226</v>
+        <f>'FLOPs to Power'!B10*(1+$B$27)^2</f>
+        <v>763.613276375</v>
       </c>
       <c r="C37">
-        <f>'FLOPs to Power'!F15</f>
-        <v>413613333333.3334</v>
+        <f>'FLOPs to Power'!F10</f>
+        <v>542746666666.6667</v>
       </c>
       <c r="D37">
-        <f>'FLOPs to Power'!E15*(1+$B$23)^7</f>
-        <v>31.0</v>
+        <f>'FLOPs to Power'!E10*(1+$B$28)^2</f>
+        <v>14.0</v>
       </c>
       <c r="E37">
-        <f>(B37*C37/D37)/(B30*C30/D30)*$B$21</f>
-        <v>618.5396053977472</v>
+        <f>(B37*C37/D37)/(B35*C35/D35)*$B$26</f>
+        <v>232.55245809233412</v>
       </c>
       <c r="F37">
-        <f>MAX(E37,F36*(1-$B$24))</f>
-        <v>618.5396053977472</v>
+        <f>MAX(E37,F36*(1-$B$29),IF(A37&gt;=$B$21,F36*(1+MIN((B37-B36)/B36,$B$32)),0))</f>
+        <v>232.55245809233412</v>
       </c>
       <c r="G37">
-        <f>G36*(1+IF(A37&lt;=2027,$B$15,IF(A37&lt;=2030,$B$16,IF(A37&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>357.65786875000003</v>
+        <f>G36*(1+IF(A37&lt;=2027,$B$16,IF(A37&lt;=2030,$B$17,IF(A37&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>104.18799999999999</v>
       </c>
       <c r="H37">
         <f>0.12+MIN(1,(A37-2025)/10)*(0.25-0.12)</f>
-        <v>0.211</v>
+        <v>0.146</v>
       </c>
       <c r="I37">
-        <f>IF(AND($B$26&gt;0,F37-G37&gt;0),MAX(H37,$B$26),H37)</f>
-        <v>0.211</v>
+        <f>IF($B$31&lt;=0.25,H37,IF(A37&lt;=$B$22,H37,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A37-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
+        <v>0.146</v>
       </c>
       <c r="J37">
         <f>F37*H37/I37</f>
-        <v>618.5396053977472</v>
+        <v>232.55245809233412</v>
       </c>
       <c r="K37">
         <f>J37-G37</f>
-        <v>260.8817366477472</v>
+        <v>128.36445809233413</v>
       </c>
       <c r="L37">
-        <f>IF(AND(A37&gt;=$B$50,K37&lt;30),A37,99999)</f>
+        <f>IF(AND(A37&gt;=$B$55,K37&lt;30),A37,99999)</f>
         <v>99999</v>
       </c>
       <c r="M37">
         <f>IF(K37&lt;0,A37,99999)</f>
         <v>99999</v>
       </c>
+      <c r="N37">
+        <f>IF(AND(A37&gt;2027,(J37-J36)/J36&lt;0.02),A37,99999)</f>
+        <v>99999</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>2033</v>
+        <v>2028</v>
       </c>
       <c r="B38">
-        <f>'FLOPs to Power'!B16*(1+$B$22)^8</f>
-        <v>7334.615906104267</v>
+        <f>'FLOPs to Power'!B11*(1+$B$27)^3</f>
+        <v>1359.8027322304688</v>
       </c>
       <c r="C38">
-        <f>'FLOPs to Power'!F16</f>
-        <v>387786666666.6667</v>
+        <f>'FLOPs to Power'!F11</f>
+        <v>516920000000.00006</v>
       </c>
       <c r="D38">
-        <f>'FLOPs to Power'!E16*(1+$B$23)^8</f>
-        <v>34.0</v>
+        <f>'FLOPs to Power'!E11*(1+$B$28)^3</f>
+        <v>18.0</v>
       </c>
       <c r="E38">
-        <f>(B38*C38/D38)/(B30*C30/D30)*$B$21</f>
-        <v>657.1577986546977</v>
+        <f>(B38*C38/D38)/(B35*C35/D35)*$B$26</f>
+        <v>306.76448216611846</v>
       </c>
       <c r="F38">
-        <f>MAX(E38,F37*(1-$B$24))</f>
-        <v>657.1577986546977</v>
+        <f>MAX(E38,F37*(1-$B$29),IF(A38&gt;=$B$21,F37*(1+MIN((B38-B37)/B37,$B$32)),0))</f>
+        <v>306.76448216611846</v>
       </c>
       <c r="G38">
-        <f>G37*(1+IF(A38&lt;=2027,$B$15,IF(A38&lt;=2030,$B$16,IF(A38&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>447.07233593750004</v>
+        <f>G37*(1+IF(A38&lt;=2027,$B$16,IF(A38&lt;=2030,$B$17,IF(A38&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>135.4444</v>
       </c>
       <c r="H38">
         <f>0.12+MIN(1,(A38-2025)/10)*(0.25-0.12)</f>
-        <v>0.224</v>
+        <v>0.159</v>
       </c>
       <c r="I38">
-        <f>IF(AND($B$26&gt;0,F38-G38&gt;0),MAX(H38,$B$26),H38)</f>
-        <v>0.224</v>
+        <f>IF($B$31&lt;=0.25,H38,IF(A38&lt;=$B$22,H38,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A38-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
+        <v>0.159</v>
       </c>
       <c r="J38">
         <f>F38*H38/I38</f>
-        <v>657.1577986546977</v>
+        <v>306.76448216611846</v>
       </c>
       <c r="K38">
         <f>J38-G38</f>
-        <v>210.08546271719763</v>
+        <v>171.32008216611845</v>
       </c>
       <c r="L38">
-        <f>IF(AND(A38&gt;=$B$50,K38&lt;30),A38,99999)</f>
+        <f>IF(AND(A38&gt;=$B$55,K38&lt;30),A38,99999)</f>
         <v>99999</v>
       </c>
       <c r="M38">
         <f>IF(K38&lt;0,A38,99999)</f>
         <v>99999</v>
       </c>
+      <c r="N38">
+        <f>IF(AND(A38&gt;2027,(J38-J37)/J37&lt;0.02),A38,99999)</f>
+        <v>99999</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>2034</v>
+        <v>2029</v>
       </c>
       <c r="B39">
-        <f>'FLOPs to Power'!B17*(1+$B$22)^9</f>
-        <v>8998.706093065295</v>
+        <f>'FLOPs to Power'!B12*(1+$B$27)^4</f>
+        <v>2172.793753804055</v>
       </c>
       <c r="C39">
-        <f>'FLOPs to Power'!F17</f>
-        <v>361960000000.00006</v>
+        <f>'FLOPs to Power'!F12</f>
+        <v>491093333333.3334</v>
       </c>
       <c r="D39">
-        <f>'FLOPs to Power'!E17*(1+$B$23)^9</f>
-        <v>37.0</v>
+        <f>'FLOPs to Power'!E12*(1+$B$28)^4</f>
+        <v>21.5</v>
       </c>
       <c r="E39">
-        <f>(B39*C39/D39)/(B30*C30/D30)*$B$21</f>
-        <v>691.5399236892711</v>
+        <f>(B39*C39/D39)/(B35*C35/D35)*$B$26</f>
+        <v>389.8723334685694</v>
       </c>
       <c r="F39">
-        <f>MAX(E39,F38*(1-$B$24))</f>
-        <v>691.5399236892711</v>
+        <f>MAX(E39,F38*(1-$B$29),IF(A39&gt;=$B$21,F38*(1+MIN((B39-B38)/B38,$B$32)),0))</f>
+        <v>389.8723334685694</v>
       </c>
       <c r="G39">
-        <f>G38*(1+IF(A39&lt;=2027,$B$15,IF(A39&lt;=2030,$B$16,IF(A39&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>558.8404199218751</v>
+        <f>G38*(1+IF(A39&lt;=2027,$B$16,IF(A39&lt;=2030,$B$17,IF(A39&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>176.07772</v>
       </c>
       <c r="H39">
         <f>0.12+MIN(1,(A39-2025)/10)*(0.25-0.12)</f>
-        <v>0.237</v>
+        <v>0.172</v>
       </c>
       <c r="I39">
-        <f>IF(AND($B$26&gt;0,F39-G39&gt;0),MAX(H39,$B$26),H39)</f>
-        <v>0.237</v>
+        <f>IF($B$31&lt;=0.25,H39,IF(A39&lt;=$B$22,H39,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A39-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
+        <v>0.172</v>
       </c>
       <c r="J39">
         <f>F39*H39/I39</f>
-        <v>691.5399236892711</v>
+        <v>389.8723334685694</v>
       </c>
       <c r="K39">
         <f>J39-G39</f>
-        <v>132.69950376739598</v>
+        <v>213.79461346856942</v>
       </c>
       <c r="L39">
-        <f>IF(AND(A39&gt;=$B$50,K39&lt;30),A39,99999)</f>
+        <f>IF(AND(A39&gt;=$B$55,K39&lt;30),A39,99999)</f>
         <v>99999</v>
       </c>
       <c r="M39">
         <f>IF(K39&lt;0,A39,99999)</f>
         <v>99999</v>
       </c>
+      <c r="N39">
+        <f>IF(AND(A39&gt;2027,(J39-J38)/J38&lt;0.02),A39,99999)</f>
+        <v>99999</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="B40">
-        <f>'FLOPs to Power'!B18*(1+$B$22)^10</f>
-        <v>10620.445661620677</v>
+        <f>'FLOPs to Power'!B13*(1+$B$27)^5</f>
+        <v>3253.5840749501463</v>
       </c>
       <c r="C40">
-        <f>'FLOPs to Power'!F18</f>
-        <v>336133333333.3334</v>
+        <f>'FLOPs to Power'!F13</f>
+        <v>465266666666.66675</v>
       </c>
       <c r="D40">
-        <f>'FLOPs to Power'!E18*(1+$B$23)^10</f>
-        <v>40.0</v>
+        <f>'FLOPs to Power'!E13*(1+$B$28)^5</f>
+        <v>25.0</v>
       </c>
       <c r="E40">
-        <f>(B40*C40/D40)/(B30*C30/D30)*$B$21</f>
-        <v>701.088215006094</v>
+        <f>(B40*C40/D40)/(B35*C35/D35)*$B$26</f>
+        <v>475.6662072622415</v>
       </c>
       <c r="F40">
-        <f>MAX(E40,F39*(1-$B$24))</f>
-        <v>701.088215006094</v>
+        <f>MAX(E40,F39*(1-$B$29),IF(A40&gt;=$B$21,F39*(1+MIN((B40-B39)/B39,$B$32)),0))</f>
+        <v>475.6662072622415</v>
       </c>
       <c r="G40">
-        <f>G39*(1+IF(A40&lt;=2027,$B$15,IF(A40&lt;=2030,$B$16,IF(A40&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>698.5505249023438</v>
+        <f>G39*(1+IF(A40&lt;=2027,$B$16,IF(A40&lt;=2030,$B$17,IF(A40&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>228.901036</v>
       </c>
       <c r="H40">
         <f>0.12+MIN(1,(A40-2025)/10)*(0.25-0.12)</f>
-        <v>0.25</v>
+        <v>0.185</v>
       </c>
       <c r="I40">
-        <f>IF(AND($B$26&gt;0,F40-G40&gt;0),MAX(H40,$B$26),H40)</f>
-        <v>0.25</v>
+        <f>IF($B$31&lt;=0.25,H40,IF(A40&lt;=$B$22,H40,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A40-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
+        <v>0.185</v>
       </c>
       <c r="J40">
         <f>F40*H40/I40</f>
-        <v>701.088215006094</v>
+        <v>475.66620726224147</v>
       </c>
       <c r="K40">
         <f>J40-G40</f>
-        <v>2.537690103750151</v>
+        <v>246.76517126224147</v>
       </c>
       <c r="L40">
-        <f>IF(AND(A40&gt;=$B$50,K40&lt;30),A40,99999)</f>
-        <v>2035</v>
+        <f>IF(AND(A40&gt;=$B$55,K40&lt;30),A40,99999)</f>
+        <v>99999</v>
       </c>
       <c r="M40">
         <f>IF(K40&lt;0,A40,99999)</f>
         <v>99999</v>
       </c>
+      <c r="N40">
+        <f>IF(AND(A40&gt;2027,(J40-J39)/J39&lt;0.02),A40,99999)</f>
+        <v>99999</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>2036</v>
+        <v>2031</v>
       </c>
       <c r="B41">
-        <f>'FLOPs to Power'!B19*(1+$B$22)^11</f>
-        <v>12433.27320756883</v>
+        <f>'FLOPs to Power'!B14*(1+$B$27)^6</f>
+        <v>4573.0374147267485</v>
       </c>
       <c r="C41">
-        <f>'FLOPs to Power'!F19</f>
-        <v>310306666666.6667</v>
+        <f>'FLOPs to Power'!F14</f>
+        <v>439440000000.0</v>
       </c>
       <c r="D41">
-        <f>'FLOPs to Power'!E19*(1+$B$23)^11</f>
-        <v>42.857142857142854</v>
+        <f>'FLOPs to Power'!E14*(1+$B$28)^6</f>
+        <v>28.0</v>
       </c>
       <c r="E41">
-        <f>(B41*C41/D41)/(B30*C30/D30)*$B$21</f>
-        <v>707.1828222825758</v>
+        <f>(B41*C41/D41)/(B35*C35/D35)*$B$26</f>
+        <v>563.7994448970002</v>
       </c>
       <c r="F41">
-        <f>MAX(E41,F40*(1-$B$24))</f>
-        <v>707.1828222825758</v>
+        <f>MAX(E41,F40*(1-$B$29),IF(A41&gt;=$B$21,F40*(1+MIN((B41-B40)/B40,$B$32)),0))</f>
+        <v>563.7994448970002</v>
       </c>
       <c r="G41">
-        <f>G40*(1+IF(A41&lt;=2027,$B$15,IF(A41&lt;=2030,$B$16,IF(A41&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>803.3331036376953</v>
+        <f>G40*(1+IF(A41&lt;=2027,$B$16,IF(A41&lt;=2030,$B$17,IF(A41&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>286.126295</v>
       </c>
       <c r="H41">
         <f>0.12+MIN(1,(A41-2025)/10)*(0.25-0.12)</f>
-        <v>0.25</v>
+        <v>0.198</v>
       </c>
       <c r="I41">
-        <f>IF(AND($B$26&gt;0,F41-G41&gt;0),MAX(H41,$B$26),H41)</f>
-        <v>0.25</v>
+        <f>IF($B$31&lt;=0.25,H41,IF(A41&lt;=$B$22,H41,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A41-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
+        <v>0.198</v>
       </c>
       <c r="J41">
         <f>F41*H41/I41</f>
-        <v>707.1828222825758</v>
+        <v>563.7994448970002</v>
       </c>
       <c r="K41">
         <f>J41-G41</f>
-        <v>-96.15028135511955</v>
+        <v>277.67314989700014</v>
       </c>
       <c r="L41">
-        <f>IF(AND(A41&gt;=$B$50,K41&lt;30),A41,99999)</f>
-        <v>2036</v>
+        <f>IF(AND(A41&gt;=$B$55,K41&lt;30),A41,99999)</f>
+        <v>99999</v>
       </c>
       <c r="M41">
         <f>IF(K41&lt;0,A41,99999)</f>
-        <v>2036</v>
+        <v>99999</v>
+      </c>
+      <c r="N41">
+        <f>IF(AND(A41&gt;2027,(J41-J40)/J40&lt;0.02),A41,99999)</f>
+        <v>99999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>2037</v>
+        <v>2032</v>
       </c>
       <c r="B42">
-        <f>'FLOPs to Power'!B20*(1+$B$22)^12</f>
-        <v>14482.722955550775</v>
+        <f>'FLOPs to Power'!B15*(1+$B$27)^7</f>
+        <v>5901.417521751226</v>
       </c>
       <c r="C42">
-        <f>'FLOPs to Power'!F20</f>
-        <v>284480000000.0</v>
+        <f>'FLOPs to Power'!F15</f>
+        <v>413613333333.3334</v>
       </c>
       <c r="D42">
-        <f>'FLOPs to Power'!E20*(1+$B$23)^12</f>
-        <v>45.714285714285715</v>
+        <f>'FLOPs to Power'!E15*(1+$B$28)^7</f>
+        <v>31.0</v>
       </c>
       <c r="E42">
-        <f>(B42*C42/D42)/(B30*C30/D30)*$B$21</f>
-        <v>707.9920134743508</v>
+        <f>(B42*C42/D42)/(B35*C35/D35)*$B$26</f>
+        <v>618.5396053977472</v>
       </c>
       <c r="F42">
-        <f>MAX(E42,F41*(1-$B$24))</f>
-        <v>707.9920134743508</v>
+        <f>MAX(E42,F41*(1-$B$29),IF(A42&gt;=$B$21,F41*(1+MIN((B42-B41)/B41,$B$32)),0))</f>
+        <v>618.5396053977472</v>
       </c>
       <c r="G42">
-        <f>G41*(1+IF(A42&lt;=2027,$B$15,IF(A42&lt;=2030,$B$16,IF(A42&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>923.8330691833496</v>
+        <f>G41*(1+IF(A42&lt;=2027,$B$16,IF(A42&lt;=2030,$B$17,IF(A42&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>357.65786875000003</v>
       </c>
       <c r="H42">
         <f>0.12+MIN(1,(A42-2025)/10)*(0.25-0.12)</f>
-        <v>0.25</v>
+        <v>0.211</v>
       </c>
       <c r="I42">
-        <f>IF(AND($B$26&gt;0,F42-G42&gt;0),MAX(H42,$B$26),H42)</f>
-        <v>0.25</v>
+        <f>IF($B$31&lt;=0.25,H42,IF(A42&lt;=$B$22,H42,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A42-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
+        <v>0.211</v>
       </c>
       <c r="J42">
         <f>F42*H42/I42</f>
-        <v>707.9920134743508</v>
+        <v>618.5396053977472</v>
       </c>
       <c r="K42">
         <f>J42-G42</f>
-        <v>-215.84105570899885</v>
+        <v>260.8817366477472</v>
       </c>
       <c r="L42">
-        <f>IF(AND(A42&gt;=$B$50,K42&lt;30),A42,99999)</f>
-        <v>2037</v>
+        <f>IF(AND(A42&gt;=$B$55,K42&lt;30),A42,99999)</f>
+        <v>99999</v>
       </c>
       <c r="M42">
         <f>IF(K42&lt;0,A42,99999)</f>
-        <v>2037</v>
+        <v>99999</v>
+      </c>
+      <c r="N42">
+        <f>IF(AND(A42&gt;2027,(J42-J41)/J41&lt;0.02),A42,99999)</f>
+        <v>99999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>2038</v>
+        <v>2033</v>
       </c>
       <c r="B43">
-        <f>'FLOPs to Power'!B21*(1+$B$22)^13</f>
-        <v>16709.132646039423</v>
+        <f>'FLOPs to Power'!B16*(1+$B$27)^8</f>
+        <v>7334.615906104267</v>
       </c>
       <c r="C43">
-        <f>'FLOPs to Power'!F21</f>
-        <v>258653333333.33337</v>
+        <f>'FLOPs to Power'!F16</f>
+        <v>387786666666.6667</v>
       </c>
       <c r="D43">
-        <f>'FLOPs to Power'!E21*(1+$B$23)^13</f>
-        <v>48.57142857142857</v>
+        <f>'FLOPs to Power'!E16*(1+$B$28)^8</f>
+        <v>34.0</v>
       </c>
       <c r="E43">
-        <f>(B43*C43/D43)/(B30*C30/D30)*$B$21</f>
-        <v>698.9875557644822</v>
+        <f>(B43*C43/D43)/(B35*C35/D35)*$B$26</f>
+        <v>657.1577986546977</v>
       </c>
       <c r="F43">
-        <f>MAX(E43,F42*(1-$B$24))</f>
-        <v>707.9920134743508</v>
+        <f>MAX(E43,F42*(1-$B$29),IF(A43&gt;=$B$21,F42*(1+MIN((B43-B42)/B42,$B$32)),0))</f>
+        <v>657.1577986546977</v>
       </c>
       <c r="G43">
-        <f>G42*(1+IF(A43&lt;=2027,$B$15,IF(A43&lt;=2030,$B$16,IF(A43&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>1062.408029560852</v>
+        <f>G42*(1+IF(A43&lt;=2027,$B$16,IF(A43&lt;=2030,$B$17,IF(A43&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>447.07233593750004</v>
       </c>
       <c r="H43">
         <f>0.12+MIN(1,(A43-2025)/10)*(0.25-0.12)</f>
-        <v>0.25</v>
+        <v>0.224</v>
       </c>
       <c r="I43">
-        <f>IF(AND($B$26&gt;0,F43-G43&gt;0),MAX(H43,$B$26),H43)</f>
-        <v>0.25</v>
+        <f>IF($B$31&lt;=0.25,H43,IF(A43&lt;=$B$22,H43,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A43-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
+        <v>0.224</v>
       </c>
       <c r="J43">
         <f>F43*H43/I43</f>
-        <v>707.9920134743508</v>
+        <v>657.1577986546977</v>
       </c>
       <c r="K43">
         <f>J43-G43</f>
-        <v>-354.41601608650114</v>
+        <v>210.08546271719763</v>
       </c>
       <c r="L43">
-        <f>IF(AND(A43&gt;=$B$50,K43&lt;30),A43,99999)</f>
-        <v>2038</v>
+        <f>IF(AND(A43&gt;=$B$55,K43&lt;30),A43,99999)</f>
+        <v>99999</v>
       </c>
       <c r="M43">
         <f>IF(K43&lt;0,A43,99999)</f>
-        <v>2038</v>
+        <v>99999</v>
+      </c>
+      <c r="N43">
+        <f>IF(AND(A43&gt;2027,(J43-J42)/J42&lt;0.02),A43,99999)</f>
+        <v>99999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="B44">
-        <f>'FLOPs to Power'!B22*(1+$B$22)^14</f>
-        <v>18373.445150193562</v>
+        <f>'FLOPs to Power'!B17*(1+$B$27)^9</f>
+        <v>8998.706093065295</v>
       </c>
       <c r="C44">
-        <f>'FLOPs to Power'!F22</f>
-        <v>232826666666.6667</v>
+        <f>'FLOPs to Power'!F17</f>
+        <v>361960000000.00006</v>
       </c>
       <c r="D44">
-        <f>'FLOPs to Power'!E22*(1+$B$23)^14</f>
-        <v>51.42857142857143</v>
+        <f>'FLOPs to Power'!E17*(1+$B$28)^9</f>
+        <v>37.0</v>
       </c>
       <c r="E44">
-        <f>(B44*C44/D44)/(B30*C30/D30)*$B$21</f>
-        <v>653.4271742029925</v>
+        <f>(B44*C44/D44)/(B35*C35/D35)*$B$26</f>
+        <v>691.5399236892711</v>
       </c>
       <c r="F44">
-        <f>MAX(E44,F43*(1-$B$24))</f>
-        <v>707.9920134743508</v>
+        <f>MAX(E44,F43*(1-$B$29),IF(A44&gt;=$B$21,F43*(1+MIN((B44-B43)/B43,$B$32)),0))</f>
+        <v>691.5399236892711</v>
       </c>
       <c r="G44">
-        <f>G43*(1+IF(A44&lt;=2027,$B$15,IF(A44&lt;=2030,$B$16,IF(A44&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>1221.7692339949797</v>
+        <f>G43*(1+IF(A44&lt;=2027,$B$16,IF(A44&lt;=2030,$B$17,IF(A44&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>558.8404199218751</v>
       </c>
       <c r="H44">
         <f>0.12+MIN(1,(A44-2025)/10)*(0.25-0.12)</f>
-        <v>0.25</v>
+        <v>0.237</v>
       </c>
       <c r="I44">
-        <f>IF(AND($B$26&gt;0,F44-G44&gt;0),MAX(H44,$B$26),H44)</f>
-        <v>0.25</v>
+        <f>IF($B$31&lt;=0.25,H44,IF(A44&lt;=$B$22,H44,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A44-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
+        <v>0.237</v>
       </c>
       <c r="J44">
         <f>F44*H44/I44</f>
-        <v>707.9920134743508</v>
+        <v>691.5399236892711</v>
       </c>
       <c r="K44">
         <f>J44-G44</f>
-        <v>-513.7772205206289</v>
+        <v>132.69950376739598</v>
       </c>
       <c r="L44">
-        <f>IF(AND(A44&gt;=$B$50,K44&lt;30),A44,99999)</f>
-        <v>2039</v>
+        <f>IF(AND(A44&gt;=$B$55,K44&lt;30),A44,99999)</f>
+        <v>99999</v>
       </c>
       <c r="M44">
         <f>IF(K44&lt;0,A44,99999)</f>
-        <v>2039</v>
+        <v>99999</v>
+      </c>
+      <c r="N44">
+        <f>IF(AND(A44&gt;2027,(J44-J43)/J43&lt;0.02),A44,99999)</f>
+        <v>99999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="B45">
-        <f>'FLOPs to Power'!B23*(1+$B$22)^15</f>
-        <v>20019.811067386545</v>
+        <f>'FLOPs to Power'!B18*(1+$B$27)^10</f>
+        <v>10620.445661620677</v>
       </c>
       <c r="C45">
-        <f>'FLOPs to Power'!F23</f>
-        <v>207000000000.00003</v>
+        <f>'FLOPs to Power'!F18</f>
+        <v>336133333333.3334</v>
       </c>
       <c r="D45">
-        <f>'FLOPs to Power'!E23*(1+$B$23)^15</f>
-        <v>54.285714285714285</v>
+        <f>'FLOPs to Power'!E18*(1+$B$28)^10</f>
+        <v>40.0</v>
       </c>
       <c r="E45">
-        <f>(B45*C45/D45)/(B30*C30/D30)*$B$21</f>
-        <v>599.684878766789</v>
+        <f>(B45*C45/D45)/(B35*C35/D35)*$B$26</f>
+        <v>701.088215006094</v>
       </c>
       <c r="F45">
-        <f>MAX(E45,F44*(1-$B$24))</f>
-        <v>707.9920134743508</v>
+        <f>MAX(E45,F44*(1-$B$29),IF(A45&gt;=$B$21,F44*(1+MIN((B45-B44)/B44,$B$32)),0))</f>
+        <v>701.088215006094</v>
       </c>
       <c r="G45">
-        <f>G44*(1+IF(A45&lt;=2027,$B$15,IF(A45&lt;=2030,$B$16,IF(A45&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>1405.0346190942266</v>
+        <f>G44*(1+IF(A45&lt;=2027,$B$16,IF(A45&lt;=2030,$B$17,IF(A45&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>698.5505249023438</v>
       </c>
       <c r="H45">
         <f>0.12+MIN(1,(A45-2025)/10)*(0.25-0.12)</f>
         <v>0.25</v>
       </c>
       <c r="I45">
-        <f>IF(AND($B$26&gt;0,F45-G45&gt;0),MAX(H45,$B$26),H45)</f>
+        <f>IF($B$31&lt;=0.25,H45,IF(A45&lt;=$B$22,H45,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A45-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.25</v>
       </c>
       <c r="J45">
         <f>F45*H45/I45</f>
-        <v>707.9920134743508</v>
+        <v>701.088215006094</v>
       </c>
       <c r="K45">
         <f>J45-G45</f>
-        <v>-697.0426056198759</v>
+        <v>2.537690103750151</v>
       </c>
       <c r="L45">
-        <f>IF(AND(A45&gt;=$B$50,K45&lt;30),A45,99999)</f>
-        <v>2040</v>
+        <f>IF(AND(A45&gt;=$B$55,K45&lt;30),A45,99999)</f>
+        <v>2035</v>
       </c>
       <c r="M45">
         <f>IF(K45&lt;0,A45,99999)</f>
-        <v>2040</v>
+        <v>99999</v>
+      </c>
+      <c r="N45">
+        <f>IF(AND(A45&gt;2027,(J45-J44)/J44&lt;0.02),A45,99999)</f>
+        <v>2035</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="B46">
-        <f>'FLOPs to Power'!B24*(1+$B$22)^16</f>
-        <v>21860.123936624695</v>
+        <f>'FLOPs to Power'!B19*(1+$B$27)^11</f>
+        <v>12433.27320756883</v>
       </c>
       <c r="C46">
-        <f>'FLOPs to Power'!F24</f>
-        <v>207000000000.00003</v>
+        <f>'FLOPs to Power'!F19</f>
+        <v>310306666666.6667</v>
       </c>
       <c r="D46">
-        <f>'FLOPs to Power'!E24*(1+$B$23)^16</f>
-        <v>57.14285714285714</v>
+        <f>'FLOPs to Power'!E19*(1+$B$28)^11</f>
+        <v>42.857142857142854</v>
       </c>
       <c r="E46">
-        <f>(B46*C46/D46)/(B30*C30/D30)*$B$21</f>
-        <v>622.0701305424171</v>
+        <f>(B46*C46/D46)/(B35*C35/D35)*$B$26</f>
+        <v>707.1828222825758</v>
       </c>
       <c r="F46">
-        <f>MAX(E46,F45*(1-$B$24))</f>
-        <v>707.9920134743508</v>
+        <f>MAX(E46,F45*(1-$B$29),IF(A46&gt;=$B$21,F45*(1+MIN((B46-B45)/B45,$B$32)),0))</f>
+        <v>707.1828222825758</v>
       </c>
       <c r="G46">
-        <f>G45*(1+IF(A46&lt;=2027,$B$15,IF(A46&lt;=2030,$B$16,IF(A46&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>1615.7898119583606</v>
+        <f>G45*(1+IF(A46&lt;=2027,$B$16,IF(A46&lt;=2030,$B$17,IF(A46&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>803.3331036376953</v>
       </c>
       <c r="H46">
         <f>0.12+MIN(1,(A46-2025)/10)*(0.25-0.12)</f>
         <v>0.25</v>
       </c>
       <c r="I46">
-        <f>IF(AND($B$26&gt;0,F46-G46&gt;0),MAX(H46,$B$26),H46)</f>
+        <f>IF($B$31&lt;=0.25,H46,IF(A46&lt;=$B$22,H46,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A46-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.25</v>
       </c>
       <c r="J46">
         <f>F46*H46/I46</f>
-        <v>707.9920134743508</v>
+        <v>707.1828222825758</v>
       </c>
       <c r="K46">
         <f>J46-G46</f>
-        <v>-907.7977984840098</v>
+        <v>-96.15028135511955</v>
       </c>
       <c r="L46">
-        <f>IF(AND(A46&gt;=$B$50,K46&lt;30),A46,99999)</f>
-        <v>2041</v>
+        <f>IF(AND(A46&gt;=$B$55,K46&lt;30),A46,99999)</f>
+        <v>2036</v>
       </c>
       <c r="M46">
         <f>IF(K46&lt;0,A46,99999)</f>
-        <v>2041</v>
+        <v>2036</v>
+      </c>
+      <c r="N46">
+        <f>IF(AND(A46&gt;2027,(J46-J45)/J45&lt;0.02),A46,99999)</f>
+        <v>2036</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>2042</v>
+        <v>2037</v>
       </c>
       <c r="B47">
-        <f>'FLOPs to Power'!B25*(1+$B$22)^17</f>
-        <v>23789.688660175238</v>
+        <f>'FLOPs to Power'!B20*(1+$B$27)^12</f>
+        <v>14482.722955550775</v>
       </c>
       <c r="C47">
-        <f>'FLOPs to Power'!F25</f>
-        <v>207000000000.00003</v>
+        <f>'FLOPs to Power'!F20</f>
+        <v>284480000000.0</v>
       </c>
       <c r="D47">
-        <f>'FLOPs to Power'!E25*(1+$B$23)^17</f>
-        <v>60.0</v>
+        <f>'FLOPs to Power'!E20*(1+$B$28)^12</f>
+        <v>45.714285714285715</v>
       </c>
       <c r="E47">
-        <f>(B47*C47/D47)/(B30*C30/D30)*$B$21</f>
-        <v>644.7423355487456</v>
+        <f>(B47*C47/D47)/(B35*C35/D35)*$B$26</f>
+        <v>707.9920134743508</v>
       </c>
       <c r="F47">
-        <f>MAX(E47,F46*(1-$B$24))</f>
+        <f>MAX(E47,F46*(1-$B$29),IF(A47&gt;=$B$21,F46*(1+MIN((B47-B46)/B46,$B$32)),0))</f>
         <v>707.9920134743508</v>
       </c>
       <c r="G47">
-        <f>G46*(1+IF(A47&lt;=2027,$B$15,IF(A47&lt;=2030,$B$16,IF(A47&lt;=2035,$B$17,$B$18)))*$B$25)</f>
-        <v>1858.1582837521146</v>
+        <f>G46*(1+IF(A47&lt;=2027,$B$16,IF(A47&lt;=2030,$B$17,IF(A47&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>923.8330691833496</v>
       </c>
       <c r="H47">
         <f>0.12+MIN(1,(A47-2025)/10)*(0.25-0.12)</f>
         <v>0.25</v>
       </c>
       <c r="I47">
-        <f>IF(AND($B$26&gt;0,F47-G47&gt;0),MAX(H47,$B$26),H47)</f>
+        <f>IF($B$31&lt;=0.25,H47,IF(A47&lt;=$B$22,H47,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A47-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.25</v>
       </c>
       <c r="J47">
@@ -20612,70 +20483,370 @@
       </c>
       <c r="K47">
         <f>J47-G47</f>
-        <v>-1150.166270277764</v>
+        <v>-215.84105570899885</v>
       </c>
       <c r="L47">
-        <f>IF(AND(A47&gt;=$B$50,K47&lt;30),A47,99999)</f>
-        <v>2042</v>
+        <f>IF(AND(A47&gt;=$B$55,K47&lt;30),A47,99999)</f>
+        <v>2037</v>
       </c>
       <c r="M47">
         <f>IF(K47&lt;0,A47,99999)</f>
+        <v>2037</v>
+      </c>
+      <c r="N47">
+        <f>IF(AND(A47&gt;2027,(J47-J46)/J46&lt;0.02),A47,99999)</f>
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>2038</v>
+      </c>
+      <c r="B48">
+        <f>'FLOPs to Power'!B21*(1+$B$27)^13</f>
+        <v>16709.132646039423</v>
+      </c>
+      <c r="C48">
+        <f>'FLOPs to Power'!F21</f>
+        <v>258653333333.33337</v>
+      </c>
+      <c r="D48">
+        <f>'FLOPs to Power'!E21*(1+$B$28)^13</f>
+        <v>48.57142857142857</v>
+      </c>
+      <c r="E48">
+        <f>(B48*C48/D48)/(B35*C35/D35)*$B$26</f>
+        <v>698.9875557644822</v>
+      </c>
+      <c r="F48">
+        <f>MAX(E48,F47*(1-$B$29),IF(A48&gt;=$B$21,F47*(1+MIN((B48-B47)/B47,$B$32)),0))</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="G48">
+        <f>G47*(1+IF(A48&lt;=2027,$B$16,IF(A48&lt;=2030,$B$17,IF(A48&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>1062.408029560852</v>
+      </c>
+      <c r="H48">
+        <f>0.12+MIN(1,(A48-2025)/10)*(0.25-0.12)</f>
+        <v>0.25</v>
+      </c>
+      <c r="I48">
+        <f>IF($B$31&lt;=0.25,H48,IF(A48&lt;=$B$22,H48,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A48-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
+        <v>0.25</v>
+      </c>
+      <c r="J48">
+        <f>F48*H48/I48</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="K48">
+        <f>J48-G48</f>
+        <v>-354.41601608650114</v>
+      </c>
+      <c r="L48">
+        <f>IF(AND(A48&gt;=$B$55,K48&lt;30),A48,99999)</f>
+        <v>2038</v>
+      </c>
+      <c r="M48">
+        <f>IF(K48&lt;0,A48,99999)</f>
+        <v>2038</v>
+      </c>
+      <c r="N48">
+        <f>IF(AND(A48&gt;2027,(J48-J47)/J47&lt;0.02),A48,99999)</f>
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>2039</v>
+      </c>
+      <c r="B49">
+        <f>'FLOPs to Power'!B22*(1+$B$27)^14</f>
+        <v>18373.445150193562</v>
+      </c>
+      <c r="C49">
+        <f>'FLOPs to Power'!F22</f>
+        <v>232826666666.6667</v>
+      </c>
+      <c r="D49">
+        <f>'FLOPs to Power'!E22*(1+$B$28)^14</f>
+        <v>51.42857142857143</v>
+      </c>
+      <c r="E49">
+        <f>(B49*C49/D49)/(B35*C35/D35)*$B$26</f>
+        <v>653.4271742029925</v>
+      </c>
+      <c r="F49">
+        <f>MAX(E49,F48*(1-$B$29),IF(A49&gt;=$B$21,F48*(1+MIN((B49-B48)/B48,$B$32)),0))</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="G49">
+        <f>G48*(1+IF(A49&lt;=2027,$B$16,IF(A49&lt;=2030,$B$17,IF(A49&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>1221.7692339949797</v>
+      </c>
+      <c r="H49">
+        <f>0.12+MIN(1,(A49-2025)/10)*(0.25-0.12)</f>
+        <v>0.25</v>
+      </c>
+      <c r="I49">
+        <f>IF($B$31&lt;=0.25,H49,IF(A49&lt;=$B$22,H49,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A49-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
+        <v>0.25</v>
+      </c>
+      <c r="J49">
+        <f>F49*H49/I49</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="K49">
+        <f>J49-G49</f>
+        <v>-513.7772205206289</v>
+      </c>
+      <c r="L49">
+        <f>IF(AND(A49&gt;=$B$55,K49&lt;30),A49,99999)</f>
+        <v>2039</v>
+      </c>
+      <c r="M49">
+        <f>IF(K49&lt;0,A49,99999)</f>
+        <v>2039</v>
+      </c>
+      <c r="N49">
+        <f>IF(AND(A49&gt;2027,(J49-J48)/J48&lt;0.02),A49,99999)</f>
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>2040</v>
+      </c>
+      <c r="B50">
+        <f>'FLOPs to Power'!B23*(1+$B$27)^15</f>
+        <v>20019.811067386545</v>
+      </c>
+      <c r="C50">
+        <f>'FLOPs to Power'!F23</f>
+        <v>207000000000.00003</v>
+      </c>
+      <c r="D50">
+        <f>'FLOPs to Power'!E23*(1+$B$28)^15</f>
+        <v>54.285714285714285</v>
+      </c>
+      <c r="E50">
+        <f>(B50*C50/D50)/(B35*C35/D35)*$B$26</f>
+        <v>599.684878766789</v>
+      </c>
+      <c r="F50">
+        <f>MAX(E50,F49*(1-$B$29),IF(A50&gt;=$B$21,F49*(1+MIN((B50-B49)/B49,$B$32)),0))</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="G50">
+        <f>G49*(1+IF(A50&lt;=2027,$B$16,IF(A50&lt;=2030,$B$17,IF(A50&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>1405.0346190942266</v>
+      </c>
+      <c r="H50">
+        <f>0.12+MIN(1,(A50-2025)/10)*(0.25-0.12)</f>
+        <v>0.25</v>
+      </c>
+      <c r="I50">
+        <f>IF($B$31&lt;=0.25,H50,IF(A50&lt;=$B$22,H50,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A50-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
+        <v>0.25</v>
+      </c>
+      <c r="J50">
+        <f>F50*H50/I50</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="K50">
+        <f>J50-G50</f>
+        <v>-697.0426056198759</v>
+      </c>
+      <c r="L50">
+        <f>IF(AND(A50&gt;=$B$55,K50&lt;30),A50,99999)</f>
+        <v>2040</v>
+      </c>
+      <c r="M50">
+        <f>IF(K50&lt;0,A50,99999)</f>
+        <v>2040</v>
+      </c>
+      <c r="N50">
+        <f>IF(AND(A50&gt;2027,(J50-J49)/J49&lt;0.02),A50,99999)</f>
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>2041</v>
+      </c>
+      <c r="B51">
+        <f>'FLOPs to Power'!B24*(1+$B$27)^16</f>
+        <v>21860.123936624695</v>
+      </c>
+      <c r="C51">
+        <f>'FLOPs to Power'!F24</f>
+        <v>207000000000.00003</v>
+      </c>
+      <c r="D51">
+        <f>'FLOPs to Power'!E24*(1+$B$28)^16</f>
+        <v>57.14285714285714</v>
+      </c>
+      <c r="E51">
+        <f>(B51*C51/D51)/(B35*C35/D35)*$B$26</f>
+        <v>622.0701305424171</v>
+      </c>
+      <c r="F51">
+        <f>MAX(E51,F50*(1-$B$29),IF(A51&gt;=$B$21,F50*(1+MIN((B51-B50)/B50,$B$32)),0))</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="G51">
+        <f>G50*(1+IF(A51&lt;=2027,$B$16,IF(A51&lt;=2030,$B$17,IF(A51&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>1615.7898119583606</v>
+      </c>
+      <c r="H51">
+        <f>0.12+MIN(1,(A51-2025)/10)*(0.25-0.12)</f>
+        <v>0.25</v>
+      </c>
+      <c r="I51">
+        <f>IF($B$31&lt;=0.25,H51,IF(A51&lt;=$B$22,H51,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A51-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
+        <v>0.25</v>
+      </c>
+      <c r="J51">
+        <f>F51*H51/I51</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="K51">
+        <f>J51-G51</f>
+        <v>-907.7977984840098</v>
+      </c>
+      <c r="L51">
+        <f>IF(AND(A51&gt;=$B$55,K51&lt;30),A51,99999)</f>
+        <v>2041</v>
+      </c>
+      <c r="M51">
+        <f>IF(K51&lt;0,A51,99999)</f>
+        <v>2041</v>
+      </c>
+      <c r="N51">
+        <f>IF(AND(A51&gt;2027,(J51-J50)/J50&lt;0.02),A51,99999)</f>
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
         <v>2042</v>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="47" t="inlineStr">
+      <c r="B52">
+        <f>'FLOPs to Power'!B25*(1+$B$27)^17</f>
+        <v>23789.688660175238</v>
+      </c>
+      <c r="C52">
+        <f>'FLOPs to Power'!F25</f>
+        <v>207000000000.00003</v>
+      </c>
+      <c r="D52">
+        <f>'FLOPs to Power'!E25*(1+$B$28)^17</f>
+        <v>60.0</v>
+      </c>
+      <c r="E52">
+        <f>(B52*C52/D52)/(B35*C35/D35)*$B$26</f>
+        <v>644.7423355487456</v>
+      </c>
+      <c r="F52">
+        <f>MAX(E52,F51*(1-$B$29),IF(A52&gt;=$B$21,F51*(1+MIN((B52-B51)/B51,$B$32)),0))</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="G52">
+        <f>G51*(1+IF(A52&lt;=2027,$B$16,IF(A52&lt;=2030,$B$17,IF(A52&lt;=2035,$B$18,$B$19)))*$B$30)</f>
+        <v>1858.1582837521146</v>
+      </c>
+      <c r="H52">
+        <f>0.12+MIN(1,(A52-2025)/10)*(0.25-0.12)</f>
+        <v>0.25</v>
+      </c>
+      <c r="I52">
+        <f>IF($B$31&lt;=0.25,H52,IF(A52&lt;=$B$22,H52,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A52-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
+        <v>0.25</v>
+      </c>
+      <c r="J52">
+        <f>F52*H52/I52</f>
+        <v>707.9920134743508</v>
+      </c>
+      <c r="K52">
+        <f>J52-G52</f>
+        <v>-1150.166270277764</v>
+      </c>
+      <c r="L52">
+        <f>IF(AND(A52&gt;=$B$55,K52&lt;30),A52,99999)</f>
+        <v>2042</v>
+      </c>
+      <c r="M52">
+        <f>IF(K52&lt;0,A52,99999)</f>
+        <v>2042</v>
+      </c>
+      <c r="N52">
+        <f>IF(AND(A52&gt;2027,(J52-J51)/J51&lt;0.02),A52,99999)</f>
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>PEAK GAP (GW)</t>
         </is>
       </c>
-      <c r="B49">
-        <f>MAX(K30:K47)</f>
+      <c r="B54">
+        <f>MAX(K35:K52)</f>
         <v>277.67314989700014</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>peak year</t>
         </is>
       </c>
-      <c r="B50">
-        <f>INDEX(A30:A47,MATCH(MAX(K30:K47),K30:K47,0))</f>
+      <c r="B55">
+        <f>INDEX(A35:A52,MATCH(MAX(K35:K52),K35:K52,0))</f>
         <v>2031</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>balance year (gap&lt;30 after peak)</t>
         </is>
       </c>
-      <c r="B51">
-        <f>IF(MIN(L30:L47)=99999,"post-2042",MIN(L30:L47))</f>
+      <c r="B56">
+        <f>IF(MIN(L35:L52)=99999,"post-2042",MIN(L35:L52))</f>
         <v>2035</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>overshoot year (gap&lt;0)</t>
         </is>
       </c>
-      <c r="B52">
-        <f>IF(MIN(M30:M47)=99999,"post-2042",MIN(M30:M47))</f>
+      <c r="B57">
+        <f>IF(MIN(M35:M52)=99999,"post-2042",MIN(M35:M52))</f>
         <v>2036</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
-          <t>demand floor 2042 (GW)</t>
+          <t>realized power 2042 (GW)</t>
         </is>
       </c>
-      <c r="B53">
-        <f>ROUND(F47,0)</f>
+      <c r="B58">
+        <f>ROUND(J52,0)</f>
         <v>708</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="47" t="inlineStr">
+        <is>
+          <t>demand asymptote year (YoY&lt;2%)</t>
+        </is>
+      </c>
+      <c r="B59">
+        <f>IF(MIN(N35:N52)=99999,"post-2042 (still climbing)",MIN(N35:N52))</f>
+        <v>2035</v>
       </c>
     </row>
   </sheetData>

--- a/Token_and_Data_Build_Out_v4_2.xlsx
+++ b/Token_and_Data_Build_Out_v4_2.xlsx
@@ -19322,11 +19322,11 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="46"/>
-    <col min="2" max="14" width="15"/>
+    <col min="2" max="16" width="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19339,7 +19339,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Set scenario in B3 (1=Bull, 2=Base, 3=Bear, 4=Central). Everything recomputes. CENTRAL = most-likely COUPLED case: second-wave agentic demand 10%/yr from 2034 AND STRUCTURAL utilization ramping 2030-&gt;2040 toward 70% (batch ceiling). Util rises WITH agentic, always-on, so the demand surge is largely absorbed: realized power flattens mid-decade, then gently resumes once the ~25%-&gt;70% utilization runway is spent.</t>
+          <t>Set scenario in B3 (1=Bull, 2=Base, 3=Bear, 4=Central). Everything recomputes. CENTRAL = most-likely COUPLED case: second-wave agentic demand 10%/yr from 2034 AND STRUCTURAL utilization ramping 2030-&gt;2040 toward 70% (batch ceiling). Util rises WITH agentic, always-on, so the demand surge is largely absorbed: realized power flattens mid-decade, then gently resumes once the ~25%-&gt;70% utilization runway is spent. ANNUAL UTILIZATION: col I = structural (auto); type a value in col J (util OVERRIDE) to flex any single year; col K = util USED feeds realized power + gap.</t>
         </is>
       </c>
     </row>
@@ -19728,30 +19728,40 @@
       </c>
       <c r="I34" s="47" t="inlineStr">
         <is>
-          <t>util structural</t>
+          <t>util structural (auto)</t>
         </is>
       </c>
       <c r="J34" s="47" t="inlineStr">
+        <is>
+          <t>util OVERRIDE (blank=auto)</t>
+        </is>
+      </c>
+      <c r="K34" s="47" t="inlineStr">
+        <is>
+          <t>util USED</t>
+        </is>
+      </c>
+      <c r="L34" s="47" t="inlineStr">
         <is>
           <t>realized power GW</t>
         </is>
       </c>
-      <c r="K34" s="47" t="inlineStr">
+      <c r="M34" s="47" t="inlineStr">
         <is>
           <t>GAP GW</t>
         </is>
       </c>
-      <c r="L34" s="47" t="inlineStr">
+      <c r="N34" s="47" t="inlineStr">
         <is>
           <t>_bal</t>
         </is>
       </c>
-      <c r="M34" s="47" t="inlineStr">
+      <c r="O34" s="47" t="inlineStr">
         <is>
           <t>_over</t>
         </is>
       </c>
-      <c r="N34" s="47" t="inlineStr">
+      <c r="P34" s="47" t="inlineStr">
         <is>
           <t>_asym</t>
         </is>
@@ -19793,23 +19803,28 @@
         <f>IF($B$31&lt;=0.25,H35,IF(A35&lt;=$B$22,H35,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A35-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.12</v>
       </c>
-      <c r="J35">
-        <f>F35*H35/I35</f>
+      <c r="J35"/>
+      <c r="K35">
+        <f>IF(ISBLANK(J35),I35,J35)</f>
+        <v>0.12</v>
+      </c>
+      <c r="L35">
+        <f>F35*H35/K35</f>
         <v>70.0</v>
       </c>
-      <c r="K35">
-        <f>J35-G35</f>
+      <c r="M35">
+        <f>L35-G35</f>
         <v>0.0</v>
       </c>
-      <c r="L35">
-        <f>IF(AND(A35&gt;=$B$55,K35&lt;30),A35,99999)</f>
+      <c r="N35">
+        <f>IF(AND(A35&gt;=$B$55,M35&lt;30),A35,99999)</f>
         <v>99999</v>
       </c>
-      <c r="M35">
-        <f>IF(K35&lt;0,A35,99999)</f>
+      <c r="O35">
+        <f>IF(M35&lt;0,A35,99999)</f>
         <v>99999</v>
       </c>
-      <c r="N35">
+      <c r="P35">
         <f>99999</f>
         <v>99999</v>
       </c>
@@ -19850,24 +19865,29 @@
         <f>IF($B$31&lt;=0.25,H36,IF(A36&lt;=$B$22,H36,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A36-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.133</v>
       </c>
-      <c r="J36">
-        <f>F36*H36/I36</f>
+      <c r="J36"/>
+      <c r="K36">
+        <f>IF(ISBLANK(J36),I36,J36)</f>
+        <v>0.133</v>
+      </c>
+      <c r="L36">
+        <f>F36*H36/K36</f>
         <v>187.12253724689498</v>
       </c>
-      <c r="K36">
-        <f>J36-G36</f>
+      <c r="M36">
+        <f>L36-G36</f>
         <v>101.72253724689499</v>
       </c>
-      <c r="L36">
-        <f>IF(AND(A36&gt;=$B$55,K36&lt;30),A36,99999)</f>
+      <c r="N36">
+        <f>IF(AND(A36&gt;=$B$55,M36&lt;30),A36,99999)</f>
         <v>99999</v>
       </c>
-      <c r="M36">
-        <f>IF(K36&lt;0,A36,99999)</f>
+      <c r="O36">
+        <f>IF(M36&lt;0,A36,99999)</f>
         <v>99999</v>
       </c>
-      <c r="N36">
-        <f>IF(AND(A36&gt;2027,(J36-J35)/J35&lt;0.02),A36,99999)</f>
+      <c r="P36">
+        <f>IF(AND(A36&gt;2027,(L36-L35)/L35&lt;0.02),A36,99999)</f>
         <v>99999</v>
       </c>
     </row>
@@ -19907,24 +19927,29 @@
         <f>IF($B$31&lt;=0.25,H37,IF(A37&lt;=$B$22,H37,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A37-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.146</v>
       </c>
-      <c r="J37">
-        <f>F37*H37/I37</f>
+      <c r="J37"/>
+      <c r="K37">
+        <f>IF(ISBLANK(J37),I37,J37)</f>
+        <v>0.146</v>
+      </c>
+      <c r="L37">
+        <f>F37*H37/K37</f>
         <v>232.55245809233412</v>
       </c>
-      <c r="K37">
-        <f>J37-G37</f>
+      <c r="M37">
+        <f>L37-G37</f>
         <v>128.36445809233413</v>
       </c>
-      <c r="L37">
-        <f>IF(AND(A37&gt;=$B$55,K37&lt;30),A37,99999)</f>
+      <c r="N37">
+        <f>IF(AND(A37&gt;=$B$55,M37&lt;30),A37,99999)</f>
         <v>99999</v>
       </c>
-      <c r="M37">
-        <f>IF(K37&lt;0,A37,99999)</f>
+      <c r="O37">
+        <f>IF(M37&lt;0,A37,99999)</f>
         <v>99999</v>
       </c>
-      <c r="N37">
-        <f>IF(AND(A37&gt;2027,(J37-J36)/J36&lt;0.02),A37,99999)</f>
+      <c r="P37">
+        <f>IF(AND(A37&gt;2027,(L37-L36)/L36&lt;0.02),A37,99999)</f>
         <v>99999</v>
       </c>
     </row>
@@ -19964,24 +19989,29 @@
         <f>IF($B$31&lt;=0.25,H38,IF(A38&lt;=$B$22,H38,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A38-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.159</v>
       </c>
-      <c r="J38">
-        <f>F38*H38/I38</f>
+      <c r="J38"/>
+      <c r="K38">
+        <f>IF(ISBLANK(J38),I38,J38)</f>
+        <v>0.159</v>
+      </c>
+      <c r="L38">
+        <f>F38*H38/K38</f>
         <v>306.76448216611846</v>
       </c>
-      <c r="K38">
-        <f>J38-G38</f>
+      <c r="M38">
+        <f>L38-G38</f>
         <v>171.32008216611845</v>
       </c>
-      <c r="L38">
-        <f>IF(AND(A38&gt;=$B$55,K38&lt;30),A38,99999)</f>
+      <c r="N38">
+        <f>IF(AND(A38&gt;=$B$55,M38&lt;30),A38,99999)</f>
         <v>99999</v>
       </c>
-      <c r="M38">
-        <f>IF(K38&lt;0,A38,99999)</f>
+      <c r="O38">
+        <f>IF(M38&lt;0,A38,99999)</f>
         <v>99999</v>
       </c>
-      <c r="N38">
-        <f>IF(AND(A38&gt;2027,(J38-J37)/J37&lt;0.02),A38,99999)</f>
+      <c r="P38">
+        <f>IF(AND(A38&gt;2027,(L38-L37)/L37&lt;0.02),A38,99999)</f>
         <v>99999</v>
       </c>
     </row>
@@ -20021,24 +20051,29 @@
         <f>IF($B$31&lt;=0.25,H39,IF(A39&lt;=$B$22,H39,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A39-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.172</v>
       </c>
-      <c r="J39">
-        <f>F39*H39/I39</f>
+      <c r="J39"/>
+      <c r="K39">
+        <f>IF(ISBLANK(J39),I39,J39)</f>
+        <v>0.172</v>
+      </c>
+      <c r="L39">
+        <f>F39*H39/K39</f>
         <v>389.8723334685694</v>
       </c>
-      <c r="K39">
-        <f>J39-G39</f>
+      <c r="M39">
+        <f>L39-G39</f>
         <v>213.79461346856942</v>
       </c>
-      <c r="L39">
-        <f>IF(AND(A39&gt;=$B$55,K39&lt;30),A39,99999)</f>
+      <c r="N39">
+        <f>IF(AND(A39&gt;=$B$55,M39&lt;30),A39,99999)</f>
         <v>99999</v>
       </c>
-      <c r="M39">
-        <f>IF(K39&lt;0,A39,99999)</f>
+      <c r="O39">
+        <f>IF(M39&lt;0,A39,99999)</f>
         <v>99999</v>
       </c>
-      <c r="N39">
-        <f>IF(AND(A39&gt;2027,(J39-J38)/J38&lt;0.02),A39,99999)</f>
+      <c r="P39">
+        <f>IF(AND(A39&gt;2027,(L39-L38)/L38&lt;0.02),A39,99999)</f>
         <v>99999</v>
       </c>
     </row>
@@ -20078,24 +20113,29 @@
         <f>IF($B$31&lt;=0.25,H40,IF(A40&lt;=$B$22,H40,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A40-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.185</v>
       </c>
-      <c r="J40">
-        <f>F40*H40/I40</f>
+      <c r="J40"/>
+      <c r="K40">
+        <f>IF(ISBLANK(J40),I40,J40)</f>
+        <v>0.185</v>
+      </c>
+      <c r="L40">
+        <f>F40*H40/K40</f>
         <v>475.66620726224147</v>
       </c>
-      <c r="K40">
-        <f>J40-G40</f>
+      <c r="M40">
+        <f>L40-G40</f>
         <v>246.76517126224147</v>
       </c>
-      <c r="L40">
-        <f>IF(AND(A40&gt;=$B$55,K40&lt;30),A40,99999)</f>
+      <c r="N40">
+        <f>IF(AND(A40&gt;=$B$55,M40&lt;30),A40,99999)</f>
         <v>99999</v>
       </c>
-      <c r="M40">
-        <f>IF(K40&lt;0,A40,99999)</f>
+      <c r="O40">
+        <f>IF(M40&lt;0,A40,99999)</f>
         <v>99999</v>
       </c>
-      <c r="N40">
-        <f>IF(AND(A40&gt;2027,(J40-J39)/J39&lt;0.02),A40,99999)</f>
+      <c r="P40">
+        <f>IF(AND(A40&gt;2027,(L40-L39)/L39&lt;0.02),A40,99999)</f>
         <v>99999</v>
       </c>
     </row>
@@ -20135,24 +20175,29 @@
         <f>IF($B$31&lt;=0.25,H41,IF(A41&lt;=$B$22,H41,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A41-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.198</v>
       </c>
-      <c r="J41">
-        <f>F41*H41/I41</f>
+      <c r="J41"/>
+      <c r="K41">
+        <f>IF(ISBLANK(J41),I41,J41)</f>
+        <v>0.198</v>
+      </c>
+      <c r="L41">
+        <f>F41*H41/K41</f>
         <v>563.7994448970002</v>
       </c>
-      <c r="K41">
-        <f>J41-G41</f>
+      <c r="M41">
+        <f>L41-G41</f>
         <v>277.67314989700014</v>
       </c>
-      <c r="L41">
-        <f>IF(AND(A41&gt;=$B$55,K41&lt;30),A41,99999)</f>
+      <c r="N41">
+        <f>IF(AND(A41&gt;=$B$55,M41&lt;30),A41,99999)</f>
         <v>99999</v>
       </c>
-      <c r="M41">
-        <f>IF(K41&lt;0,A41,99999)</f>
+      <c r="O41">
+        <f>IF(M41&lt;0,A41,99999)</f>
         <v>99999</v>
       </c>
-      <c r="N41">
-        <f>IF(AND(A41&gt;2027,(J41-J40)/J40&lt;0.02),A41,99999)</f>
+      <c r="P41">
+        <f>IF(AND(A41&gt;2027,(L41-L40)/L40&lt;0.02),A41,99999)</f>
         <v>99999</v>
       </c>
     </row>
@@ -20192,24 +20237,29 @@
         <f>IF($B$31&lt;=0.25,H42,IF(A42&lt;=$B$22,H42,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A42-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.211</v>
       </c>
-      <c r="J42">
-        <f>F42*H42/I42</f>
+      <c r="J42"/>
+      <c r="K42">
+        <f>IF(ISBLANK(J42),I42,J42)</f>
+        <v>0.211</v>
+      </c>
+      <c r="L42">
+        <f>F42*H42/K42</f>
         <v>618.5396053977472</v>
       </c>
-      <c r="K42">
-        <f>J42-G42</f>
+      <c r="M42">
+        <f>L42-G42</f>
         <v>260.8817366477472</v>
       </c>
-      <c r="L42">
-        <f>IF(AND(A42&gt;=$B$55,K42&lt;30),A42,99999)</f>
+      <c r="N42">
+        <f>IF(AND(A42&gt;=$B$55,M42&lt;30),A42,99999)</f>
         <v>99999</v>
       </c>
-      <c r="M42">
-        <f>IF(K42&lt;0,A42,99999)</f>
+      <c r="O42">
+        <f>IF(M42&lt;0,A42,99999)</f>
         <v>99999</v>
       </c>
-      <c r="N42">
-        <f>IF(AND(A42&gt;2027,(J42-J41)/J41&lt;0.02),A42,99999)</f>
+      <c r="P42">
+        <f>IF(AND(A42&gt;2027,(L42-L41)/L41&lt;0.02),A42,99999)</f>
         <v>99999</v>
       </c>
     </row>
@@ -20249,24 +20299,29 @@
         <f>IF($B$31&lt;=0.25,H43,IF(A43&lt;=$B$22,H43,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A43-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.224</v>
       </c>
-      <c r="J43">
-        <f>F43*H43/I43</f>
+      <c r="J43"/>
+      <c r="K43">
+        <f>IF(ISBLANK(J43),I43,J43)</f>
+        <v>0.224</v>
+      </c>
+      <c r="L43">
+        <f>F43*H43/K43</f>
         <v>657.1577986546977</v>
       </c>
-      <c r="K43">
-        <f>J43-G43</f>
+      <c r="M43">
+        <f>L43-G43</f>
         <v>210.08546271719763</v>
       </c>
-      <c r="L43">
-        <f>IF(AND(A43&gt;=$B$55,K43&lt;30),A43,99999)</f>
+      <c r="N43">
+        <f>IF(AND(A43&gt;=$B$55,M43&lt;30),A43,99999)</f>
         <v>99999</v>
       </c>
-      <c r="M43">
-        <f>IF(K43&lt;0,A43,99999)</f>
+      <c r="O43">
+        <f>IF(M43&lt;0,A43,99999)</f>
         <v>99999</v>
       </c>
-      <c r="N43">
-        <f>IF(AND(A43&gt;2027,(J43-J42)/J42&lt;0.02),A43,99999)</f>
+      <c r="P43">
+        <f>IF(AND(A43&gt;2027,(L43-L42)/L42&lt;0.02),A43,99999)</f>
         <v>99999</v>
       </c>
     </row>
@@ -20306,24 +20361,29 @@
         <f>IF($B$31&lt;=0.25,H44,IF(A44&lt;=$B$22,H44,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A44-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.237</v>
       </c>
-      <c r="J44">
-        <f>F44*H44/I44</f>
+      <c r="J44"/>
+      <c r="K44">
+        <f>IF(ISBLANK(J44),I44,J44)</f>
+        <v>0.237</v>
+      </c>
+      <c r="L44">
+        <f>F44*H44/K44</f>
         <v>691.5399236892711</v>
       </c>
-      <c r="K44">
-        <f>J44-G44</f>
+      <c r="M44">
+        <f>L44-G44</f>
         <v>132.69950376739598</v>
       </c>
-      <c r="L44">
-        <f>IF(AND(A44&gt;=$B$55,K44&lt;30),A44,99999)</f>
+      <c r="N44">
+        <f>IF(AND(A44&gt;=$B$55,M44&lt;30),A44,99999)</f>
         <v>99999</v>
       </c>
-      <c r="M44">
-        <f>IF(K44&lt;0,A44,99999)</f>
+      <c r="O44">
+        <f>IF(M44&lt;0,A44,99999)</f>
         <v>99999</v>
       </c>
-      <c r="N44">
-        <f>IF(AND(A44&gt;2027,(J44-J43)/J43&lt;0.02),A44,99999)</f>
+      <c r="P44">
+        <f>IF(AND(A44&gt;2027,(L44-L43)/L43&lt;0.02),A44,99999)</f>
         <v>99999</v>
       </c>
     </row>
@@ -20363,24 +20423,29 @@
         <f>IF($B$31&lt;=0.25,H45,IF(A45&lt;=$B$22,H45,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A45-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.25</v>
       </c>
-      <c r="J45">
-        <f>F45*H45/I45</f>
+      <c r="J45"/>
+      <c r="K45">
+        <f>IF(ISBLANK(J45),I45,J45)</f>
+        <v>0.25</v>
+      </c>
+      <c r="L45">
+        <f>F45*H45/K45</f>
         <v>701.088215006094</v>
       </c>
-      <c r="K45">
-        <f>J45-G45</f>
+      <c r="M45">
+        <f>L45-G45</f>
         <v>2.537690103750151</v>
       </c>
-      <c r="L45">
-        <f>IF(AND(A45&gt;=$B$55,K45&lt;30),A45,99999)</f>
+      <c r="N45">
+        <f>IF(AND(A45&gt;=$B$55,M45&lt;30),A45,99999)</f>
         <v>2035</v>
       </c>
-      <c r="M45">
-        <f>IF(K45&lt;0,A45,99999)</f>
+      <c r="O45">
+        <f>IF(M45&lt;0,A45,99999)</f>
         <v>99999</v>
       </c>
-      <c r="N45">
-        <f>IF(AND(A45&gt;2027,(J45-J44)/J44&lt;0.02),A45,99999)</f>
+      <c r="P45">
+        <f>IF(AND(A45&gt;2027,(L45-L44)/L44&lt;0.02),A45,99999)</f>
         <v>2035</v>
       </c>
     </row>
@@ -20420,24 +20485,29 @@
         <f>IF($B$31&lt;=0.25,H46,IF(A46&lt;=$B$22,H46,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A46-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.25</v>
       </c>
-      <c r="J46">
-        <f>F46*H46/I46</f>
+      <c r="J46"/>
+      <c r="K46">
+        <f>IF(ISBLANK(J46),I46,J46)</f>
+        <v>0.25</v>
+      </c>
+      <c r="L46">
+        <f>F46*H46/K46</f>
         <v>707.1828222825758</v>
       </c>
-      <c r="K46">
-        <f>J46-G46</f>
+      <c r="M46">
+        <f>L46-G46</f>
         <v>-96.15028135511955</v>
       </c>
-      <c r="L46">
-        <f>IF(AND(A46&gt;=$B$55,K46&lt;30),A46,99999)</f>
+      <c r="N46">
+        <f>IF(AND(A46&gt;=$B$55,M46&lt;30),A46,99999)</f>
         <v>2036</v>
       </c>
-      <c r="M46">
-        <f>IF(K46&lt;0,A46,99999)</f>
+      <c r="O46">
+        <f>IF(M46&lt;0,A46,99999)</f>
         <v>2036</v>
       </c>
-      <c r="N46">
-        <f>IF(AND(A46&gt;2027,(J46-J45)/J45&lt;0.02),A46,99999)</f>
+      <c r="P46">
+        <f>IF(AND(A46&gt;2027,(L46-L45)/L45&lt;0.02),A46,99999)</f>
         <v>2036</v>
       </c>
     </row>
@@ -20477,24 +20547,29 @@
         <f>IF($B$31&lt;=0.25,H47,IF(A47&lt;=$B$22,H47,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A47-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.25</v>
       </c>
-      <c r="J47">
-        <f>F47*H47/I47</f>
+      <c r="J47"/>
+      <c r="K47">
+        <f>IF(ISBLANK(J47),I47,J47)</f>
+        <v>0.25</v>
+      </c>
+      <c r="L47">
+        <f>F47*H47/K47</f>
         <v>707.9920134743508</v>
       </c>
-      <c r="K47">
-        <f>J47-G47</f>
+      <c r="M47">
+        <f>L47-G47</f>
         <v>-215.84105570899885</v>
       </c>
-      <c r="L47">
-        <f>IF(AND(A47&gt;=$B$55,K47&lt;30),A47,99999)</f>
+      <c r="N47">
+        <f>IF(AND(A47&gt;=$B$55,M47&lt;30),A47,99999)</f>
         <v>2037</v>
       </c>
-      <c r="M47">
-        <f>IF(K47&lt;0,A47,99999)</f>
+      <c r="O47">
+        <f>IF(M47&lt;0,A47,99999)</f>
         <v>2037</v>
       </c>
-      <c r="N47">
-        <f>IF(AND(A47&gt;2027,(J47-J46)/J46&lt;0.02),A47,99999)</f>
+      <c r="P47">
+        <f>IF(AND(A47&gt;2027,(L47-L46)/L46&lt;0.02),A47,99999)</f>
         <v>2037</v>
       </c>
     </row>
@@ -20534,24 +20609,29 @@
         <f>IF($B$31&lt;=0.25,H48,IF(A48&lt;=$B$22,H48,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A48-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.25</v>
       </c>
-      <c r="J48">
-        <f>F48*H48/I48</f>
+      <c r="J48"/>
+      <c r="K48">
+        <f>IF(ISBLANK(J48),I48,J48)</f>
+        <v>0.25</v>
+      </c>
+      <c r="L48">
+        <f>F48*H48/K48</f>
         <v>707.9920134743508</v>
       </c>
-      <c r="K48">
-        <f>J48-G48</f>
+      <c r="M48">
+        <f>L48-G48</f>
         <v>-354.41601608650114</v>
       </c>
-      <c r="L48">
-        <f>IF(AND(A48&gt;=$B$55,K48&lt;30),A48,99999)</f>
+      <c r="N48">
+        <f>IF(AND(A48&gt;=$B$55,M48&lt;30),A48,99999)</f>
         <v>2038</v>
       </c>
-      <c r="M48">
-        <f>IF(K48&lt;0,A48,99999)</f>
+      <c r="O48">
+        <f>IF(M48&lt;0,A48,99999)</f>
         <v>2038</v>
       </c>
-      <c r="N48">
-        <f>IF(AND(A48&gt;2027,(J48-J47)/J47&lt;0.02),A48,99999)</f>
+      <c r="P48">
+        <f>IF(AND(A48&gt;2027,(L48-L47)/L47&lt;0.02),A48,99999)</f>
         <v>2038</v>
       </c>
     </row>
@@ -20591,24 +20671,29 @@
         <f>IF($B$31&lt;=0.25,H49,IF(A49&lt;=$B$22,H49,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A49-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.25</v>
       </c>
-      <c r="J49">
-        <f>F49*H49/I49</f>
+      <c r="J49"/>
+      <c r="K49">
+        <f>IF(ISBLANK(J49),I49,J49)</f>
+        <v>0.25</v>
+      </c>
+      <c r="L49">
+        <f>F49*H49/K49</f>
         <v>707.9920134743508</v>
       </c>
-      <c r="K49">
-        <f>J49-G49</f>
+      <c r="M49">
+        <f>L49-G49</f>
         <v>-513.7772205206289</v>
       </c>
-      <c r="L49">
-        <f>IF(AND(A49&gt;=$B$55,K49&lt;30),A49,99999)</f>
+      <c r="N49">
+        <f>IF(AND(A49&gt;=$B$55,M49&lt;30),A49,99999)</f>
         <v>2039</v>
       </c>
-      <c r="M49">
-        <f>IF(K49&lt;0,A49,99999)</f>
+      <c r="O49">
+        <f>IF(M49&lt;0,A49,99999)</f>
         <v>2039</v>
       </c>
-      <c r="N49">
-        <f>IF(AND(A49&gt;2027,(J49-J48)/J48&lt;0.02),A49,99999)</f>
+      <c r="P49">
+        <f>IF(AND(A49&gt;2027,(L49-L48)/L48&lt;0.02),A49,99999)</f>
         <v>2039</v>
       </c>
     </row>
@@ -20648,24 +20733,29 @@
         <f>IF($B$31&lt;=0.25,H50,IF(A50&lt;=$B$22,H50,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A50-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.25</v>
       </c>
-      <c r="J50">
-        <f>F50*H50/I50</f>
+      <c r="J50"/>
+      <c r="K50">
+        <f>IF(ISBLANK(J50),I50,J50)</f>
+        <v>0.25</v>
+      </c>
+      <c r="L50">
+        <f>F50*H50/K50</f>
         <v>707.9920134743508</v>
       </c>
-      <c r="K50">
-        <f>J50-G50</f>
+      <c r="M50">
+        <f>L50-G50</f>
         <v>-697.0426056198759</v>
       </c>
-      <c r="L50">
-        <f>IF(AND(A50&gt;=$B$55,K50&lt;30),A50,99999)</f>
+      <c r="N50">
+        <f>IF(AND(A50&gt;=$B$55,M50&lt;30),A50,99999)</f>
         <v>2040</v>
       </c>
-      <c r="M50">
-        <f>IF(K50&lt;0,A50,99999)</f>
+      <c r="O50">
+        <f>IF(M50&lt;0,A50,99999)</f>
         <v>2040</v>
       </c>
-      <c r="N50">
-        <f>IF(AND(A50&gt;2027,(J50-J49)/J49&lt;0.02),A50,99999)</f>
+      <c r="P50">
+        <f>IF(AND(A50&gt;2027,(L50-L49)/L49&lt;0.02),A50,99999)</f>
         <v>2040</v>
       </c>
     </row>
@@ -20705,24 +20795,29 @@
         <f>IF($B$31&lt;=0.25,H51,IF(A51&lt;=$B$22,H51,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A51-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.25</v>
       </c>
-      <c r="J51">
-        <f>F51*H51/I51</f>
+      <c r="J51"/>
+      <c r="K51">
+        <f>IF(ISBLANK(J51),I51,J51)</f>
+        <v>0.25</v>
+      </c>
+      <c r="L51">
+        <f>F51*H51/K51</f>
         <v>707.9920134743508</v>
       </c>
-      <c r="K51">
-        <f>J51-G51</f>
+      <c r="M51">
+        <f>L51-G51</f>
         <v>-907.7977984840098</v>
       </c>
-      <c r="L51">
-        <f>IF(AND(A51&gt;=$B$55,K51&lt;30),A51,99999)</f>
+      <c r="N51">
+        <f>IF(AND(A51&gt;=$B$55,M51&lt;30),A51,99999)</f>
         <v>2041</v>
       </c>
-      <c r="M51">
-        <f>IF(K51&lt;0,A51,99999)</f>
+      <c r="O51">
+        <f>IF(M51&lt;0,A51,99999)</f>
         <v>2041</v>
       </c>
-      <c r="N51">
-        <f>IF(AND(A51&gt;2027,(J51-J50)/J50&lt;0.02),A51,99999)</f>
+      <c r="P51">
+        <f>IF(AND(A51&gt;2027,(L51-L50)/L50&lt;0.02),A51,99999)</f>
         <v>2041</v>
       </c>
     </row>
@@ -20762,24 +20857,29 @@
         <f>IF($B$31&lt;=0.25,H52,IF(A52&lt;=$B$22,H52,(0.12+MIN(1,($B$22-2025)/10)*0.13)+MIN(1,(A52-$B$22)/($B$23-$B$22))*($B$31-(0.12+MIN(1,($B$22-2025)/10)*0.13))))</f>
         <v>0.25</v>
       </c>
-      <c r="J52">
-        <f>F52*H52/I52</f>
+      <c r="J52"/>
+      <c r="K52">
+        <f>IF(ISBLANK(J52),I52,J52)</f>
+        <v>0.25</v>
+      </c>
+      <c r="L52">
+        <f>F52*H52/K52</f>
         <v>707.9920134743508</v>
       </c>
-      <c r="K52">
-        <f>J52-G52</f>
+      <c r="M52">
+        <f>L52-G52</f>
         <v>-1150.166270277764</v>
       </c>
-      <c r="L52">
-        <f>IF(AND(A52&gt;=$B$55,K52&lt;30),A52,99999)</f>
+      <c r="N52">
+        <f>IF(AND(A52&gt;=$B$55,M52&lt;30),A52,99999)</f>
         <v>2042</v>
       </c>
-      <c r="M52">
-        <f>IF(K52&lt;0,A52,99999)</f>
+      <c r="O52">
+        <f>IF(M52&lt;0,A52,99999)</f>
         <v>2042</v>
       </c>
-      <c r="N52">
-        <f>IF(AND(A52&gt;2027,(J52-J51)/J51&lt;0.02),A52,99999)</f>
+      <c r="P52">
+        <f>IF(AND(A52&gt;2027,(L52-L51)/L51&lt;0.02),A52,99999)</f>
         <v>2042</v>
       </c>
     </row>
@@ -20790,7 +20890,7 @@
         </is>
       </c>
       <c r="B54">
-        <f>MAX(K35:K52)</f>
+        <f>MAX(M35:M52)</f>
         <v>277.67314989700014</v>
       </c>
     </row>
@@ -20801,7 +20901,7 @@
         </is>
       </c>
       <c r="B55">
-        <f>INDEX(A35:A52,MATCH(MAX(K35:K52),K35:K52,0))</f>
+        <f>INDEX(A35:A52,MATCH(MAX(M35:M52),M35:M52,0))</f>
         <v>2031</v>
       </c>
     </row>
@@ -20812,7 +20912,7 @@
         </is>
       </c>
       <c r="B56">
-        <f>IF(MIN(L35:L52)=99999,"post-2042",MIN(L35:L52))</f>
+        <f>IF(MIN(N35:N52)=99999,"post-2042",MIN(N35:N52))</f>
         <v>2035</v>
       </c>
     </row>
@@ -20823,7 +20923,7 @@
         </is>
       </c>
       <c r="B57">
-        <f>IF(MIN(M35:M52)=99999,"post-2042",MIN(M35:M52))</f>
+        <f>IF(MIN(O35:O52)=99999,"post-2042",MIN(O35:O52))</f>
         <v>2036</v>
       </c>
     </row>
@@ -20834,7 +20934,7 @@
         </is>
       </c>
       <c r="B58">
-        <f>ROUND(J52,0)</f>
+        <f>ROUND(L52,0)</f>
         <v>708</v>
       </c>
     </row>
@@ -20845,7 +20945,7 @@
         </is>
       </c>
       <c r="B59">
-        <f>IF(MIN(N35:N52)=99999,"post-2042 (still climbing)",MIN(N35:N52))</f>
+        <f>IF(MIN(P35:P52)=99999,"post-2042 (still climbing)",MIN(P35:P52))</f>
         <v>2035</v>
       </c>
     </row>
